--- a/results/job_matches_2026-05-12.xlsx
+++ b/results/job_matches_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Benchmark Solutions LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1df3e0ee29922c</t>
+          <t>https://www.indeed.com/viewjob?jk=f8cfebbb7e871628</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark, Scala</t>
+          <t>IAM, RDS, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6fb94b58173aba</t>
+          <t>https://www.indeed.com/viewjob?jk=0f1df3e0ee29922c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - ML/AI Data Platform (Remote)</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FEI Systems</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, Step Functions, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,124 +706,124 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58ce81b6255bf6b</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6fb94b58173aba</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Senior Systems Engineer, UDS Data Management - East</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171403dbdac6e42f</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1f7dab55752b3e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5378ca2d10086b6</t>
+          <t>https://www.indeed.com/viewjob?jk=50d8317116e3b8b4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Python)</t>
+          <t>Data Engineer - ML/AI Data Platform (Remote)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FEI Systems</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Kinesis, Athena, Step Functions, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92240e7a4713a4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a58ce81b6255bf6b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Platform &amp; DevOps Engineer</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Azure, Spark, PySpark, Scala, Kafka, Polars</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fc55dd920ed33e</t>
+          <t>https://www.indeed.com/viewjob?jk=171403dbdac6e42f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Development (Python)</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MS Excel</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c572e92f87a5b7a6</t>
+          <t>https://www.indeed.com/viewjob?jk=d5378ca2d10086b6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist - Machine Learning</t>
+          <t>AI/ML Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, Glue, Athena, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd4b842829eab81b</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a2a750b8d45131</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
+          <t>Sr Platform &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Softengine</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
+          <t>AWS, Lambda, S3, SQS, Azure, Spark, PySpark, Scala, Kafka, Polars</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,42 +951,42 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=055c54c5a52e97d2</t>
+          <t>https://www.indeed.com/viewjob?jk=03fc55dd920ed33e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Microsoft SQL Server/ETL Developer w/SSIS experience [On-Site]</t>
+          <t>Data Scientist - Machine Learning</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b9c004dc5445b</t>
+          <t>https://www.indeed.com/viewjob?jk=dd4b842829eab81b</t>
         </is>
       </c>
     </row>
@@ -1016,29 +1016,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71de8a1a6ca38c9</t>
+          <t>https://www.indeed.com/viewjob?jk=0d24c78be0131037</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Softengine</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e129ef424b7bb1</t>
+          <t>https://www.indeed.com/viewjob?jk=055c54c5a52e97d2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Development (Python)</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1081,69 +1081,69 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d0d3f0e671eca1f</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e129ef424b7bb1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8df2488699249b</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4aca5f146dc1fe</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Cloud Dev</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Transmedics</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e8c40e8e2c57109</t>
+          <t>https://www.indeed.com/viewjob?jk=c6cbe9c6196981eb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837e9f344d302e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9d37985c0bdcf2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DNS Solutions Inc.</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,19 +1231,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7663c2a8691261bd</t>
+          <t>https://www.indeed.com/viewjob?jk=837e9f344d302e6d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>DNS Solutions Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a58cf7cc708c832</t>
+          <t>https://www.indeed.com/viewjob?jk=7663c2a8691261bd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca8e86ee6ca254d</t>
+          <t>https://www.indeed.com/viewjob?jk=5a58cf7cc708c832</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b111e44c034f266</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca8e86ee6ca254d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Fully Remote!</t>
+          <t>IT Specialist/Systems Administrator</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KinderCare Learning Companies</t>
+          <t>Customer Care First</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Syracuse, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b630719ad31d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6d93d88b6a0a66</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer (AWS/Azure/GCP | Hybrid Cloud | AI Security)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LifeScale Analytics</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=187fb1dba54e59d2</t>
+          <t>https://www.indeed.com/viewjob?jk=9216704e953a3254</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer - Management and Operations (Remote in US)</t>
+          <t>Senior Cloud Security Engineer (AWS/Azure/GCP | Hybrid Cloud | AI Security)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>LifeScale Analytics</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126895852cc1414c</t>
+          <t>https://www.indeed.com/viewjob?jk=187fb1dba54e59d2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer - Fully Remote!</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>KinderCare Learning Companies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
+          <t>https://www.indeed.com/viewjob?jk=38b630719ad31d3a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Senior Cloud &amp; Backend Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ASU Preparatory Academy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, Hadoop, Hive, Spark</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=4c86711a678b9cfb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GCP ML Engineer (Vertex AI)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Storable</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Spark</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce22f8b356b35619</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb2c0deb86004e8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>GCP Cloud Engineer - Management and Operations (Remote in US)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NEXON America</t>
+          <t>Resultant</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Splunk, Jenkins</t>
+          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
+          <t>https://www.indeed.com/viewjob?jk=126895852cc1414c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff92c7be8a4ed26f</t>
+          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Santa Cruz, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e946f43c0ce5053</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer, Market Data New</t>
+          <t>GCP ML Engineer (Vertex AI)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MIO Partners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, RDS, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,94 +1686,94 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ce8c2bb2e05265</t>
+          <t>https://www.indeed.com/viewjob?jk=ce22f8b356b35619</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Santa Cruz, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
+          <t>https://www.indeed.com/viewjob?jk=8429c2a459d3de4f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Inspire11</t>
+          <t>NEXON America</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcac04dbf474e01b</t>
+          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Santa Cruz, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44f16ef92378b0</t>
+          <t>https://www.indeed.com/viewjob?jk=1e946f43c0ce5053</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Data Engineer, Market Data New</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MIO Partners</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, RDS, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2be041ba7dd258</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ce8c2bb2e05265</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Santa Cruz, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf763802f514ac89</t>
+          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Inspire11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7c3880bf1468af</t>
+          <t>https://www.indeed.com/viewjob?jk=fcac04dbf474e01b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Front-End Growth Engineer</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EvaFi</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658e57cd8469a251</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44f16ef92378b0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26d7493c6bd8679</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2be041ba7dd258</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Scala, Snowflake, MLOps</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c13da2a0f601ffa5</t>
+          <t>https://www.indeed.com/viewjob?jk=cf763802f514ac89</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, API Gateway, Azure, Data Factory, Databricks, Scala, ETL, ELT</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7c3880bf1468af</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4249a3228aea17d</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad13b87eac68b71</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Front-End Growth Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>EvaFi</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2af3b2ea12351135</t>
+          <t>https://www.indeed.com/viewjob?jk=658e57cd8469a251</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55dd6036cf4386c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c26d7493c6bd8679</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
+          <t>https://www.indeed.com/viewjob?jk=c13da2a0f601ffa5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, EMR, Lambda, API Gateway, Azure, Data Factory, Databricks, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Java Developer with Payments – R01564829</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b028c72e4fead57</t>
+          <t>https://www.indeed.com/viewjob?jk=b4249a3228aea17d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Data Engineer, Pro360 Product Group</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Hadoop, Scala, SQL Server, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70cf81a93ee7ae14</t>
+          <t>https://www.indeed.com/viewjob?jk=b0bc6c388f4a159c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Engineer Senior</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, ETL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5e0df0ff0f2609</t>
+          <t>https://www.indeed.com/viewjob?jk=70cf81a93ee7ae14</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full stack</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,42 +2341,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a4c233ec9d2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=2af3b2ea12351135</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer – Cloud and AI</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01f85e7d7e897954</t>
+          <t>https://www.indeed.com/viewjob?jk=55dd6036cf4386c2</t>
         </is>
       </c>
     </row>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,102 +2456,102 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43fdee7cf569751d</t>
+          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior MLOps &amp; Data Systems Engineer</t>
+          <t>Sales/Solutions Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lime</t>
+          <t>Artie</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e97637d29d64b4</t>
+          <t>https://www.indeed.com/viewjob?jk=50c1fe1287b79994</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Platform Architect - AI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, Flume, Spark, Scala, Kafka, Jenkins, Maven</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8925c0b6808e2ef8</t>
+          <t>https://www.indeed.com/viewjob?jk=57c71c270f4f024f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Native Java Developer (U.S. remote)</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Railroad19</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, Scala, Oracle, MySQL, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c864309c5f175c3e</t>
+          <t>https://www.indeed.com/viewjob?jk=4f670c120137d065</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer Senior</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Teton Ridge</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, ETL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9736ba6473e4804f</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5e0df0ff0f2609</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Software Engineer III - UnderwritingCenter</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f52b7af2ce28a8</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4f413a4cd84f6f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Software Engineer 2 - Full stack</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BeyondTrust</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e471f407b19da8</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a4c233ec9d2bd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Git</t>
+          <t>IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f52b7af2ce28a8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Remote / Project-Based Data Engineer for Public-Sector Data Modernization, Dashboards, and AI-Ready</t>
+          <t>Data Engineer – Cloud and AI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, PostgreSQL, MySQL, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f000f4be342c4377</t>
+          <t>https://www.indeed.com/viewjob?jk=01f85e7d7e897954</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Serenity Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fffc235cb241e45</t>
+          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2792,11 +2792,11 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,102 +2806,102 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f39f88a9b70f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=43fdee7cf569751d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Avature</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ec2088a10dc04e</t>
+          <t>https://www.indeed.com/viewjob?jk=04f0d7f99a5b402c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, Flume, Spark, Scala, Kafka, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f2031edb48e342e</t>
+          <t>https://www.indeed.com/viewjob?jk=8925c0b6808e2ef8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Solution Architect with Presales Experience</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>OJUSLLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc46a93049506224</t>
+          <t>https://www.indeed.com/viewjob?jk=43dbc51a5868e325</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Cloud Native Java Developer (U.S. remote)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Railroad19</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, Scala, Oracle, MySQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc004557d9736a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=c864309c5f175c3e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - ADF &amp; Databricks</t>
+          <t>Senior Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, NoSQL, CI/CD, Jenkins, GitHub Actions, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f3a914de107c82</t>
+          <t>https://www.indeed.com/viewjob?jk=24fe9813b60c6c14</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>BeyondTrust</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=490033b77e24b17c</t>
+          <t>https://www.indeed.com/viewjob?jk=12e471f407b19da8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Teton Ridge</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56229e27f5c6fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=9736ba6473e4804f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Oracle, PostgreSQL, MongoDB, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c41862eb239f163</t>
+          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer</t>
+          <t>Software Developer (Systems Software) - TS/SCI w/ Polygraph</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Babylon, NY, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Hive, Scala, ETL, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d3d24d3399d0363</t>
+          <t>https://www.indeed.com/viewjob?jk=b918f48362f41a28</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SmartAdvocate</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Jenkins</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=001c431f02e0a7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=8d09fe840e33b4c7</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Developer – Intelligent Systems &amp; Integrations</t>
+          <t>Remote / Project-Based Data Engineer for Public-Sector Data Modernization, Dashboards, and AI-Ready</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, PostgreSQL, MySQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5727dfe812017a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=f000f4be342c4377</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Scientist &amp; Modeler</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Iberdrola Group</t>
+          <t>Serenity Healthcare</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Orange, CT, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39fab587fb046739</t>
+          <t>https://www.indeed.com/viewjob?jk=9fffc235cb241e45</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Glencore</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, CI/CD, GitHub Actions, Docker, Airflow, Git</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0439c2a3373376b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f39f88a9b70f0a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, MLOps, CI/CD, Jenkins, Maven, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ba35ddf0464dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=29ec2088a10dc04e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff9c5f258d04aaa</t>
+          <t>https://www.indeed.com/viewjob?jk=0f2031edb48e342e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>OJUSLLC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410c7062135208be</t>
+          <t>https://www.indeed.com/viewjob?jk=fc46a93049506224</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Scientist (944)</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ABC Supply Co., Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,15 +3391,470 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc004557d9736a0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - ADF &amp; Databricks</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SYSTECH USA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5f3a914de107c82</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior AWS Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Plymouth Rock Assurance</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=490033b77e24b17c</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e56229e27f5c6fd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>hatch IT</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Oracle, PostgreSQL, MongoDB, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c41862eb239f163</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Product Software Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Wolters Kluwer</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Babylon, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d3d24d3399d0363</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Azure Data Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Power BI, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc9af17a3ab15e53</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>AI DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SmartAdvocate</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Melville, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=001c431f02e0a7d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Software Developer – Intelligent Systems &amp; Integrations</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5727dfe812017a7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist &amp; Modeler</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Iberdrola Group</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Orange, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39fab587fb046739</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, ECS, Azure, MLOps, CI/CD, Jenkins, Maven, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1ba35ddf0464dd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ff9c5f258d04aaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=410c7062135208be</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Data Scientist (944)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ABC Supply Co., Inc.</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>RDS, Azure, Databricks, ETL, ELT, Tableau, MLOps, MLflow, Git, Python</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a2beae7f9c463995</t>
         </is>

--- a/results/job_matches_2026-05-12.xlsx
+++ b/results/job_matches_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Engineer - Payments Modernization</t>
+          <t>Expert AI &amp; Cloud Development Architect - Office of the CTO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Kinesis, S3, SQS, API Gateway, IAM, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f7aa9808e3bc85</t>
+          <t>https://www.indeed.com/viewjob?jk=dcc8674d85a442c8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Senior Engineer - Payments Modernization</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Oregon State University</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Corvallis, OR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933518dacc920f09</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f7aa9808e3bc85</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Oregon State University</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Corvallis, OR, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaeff5e1c81b908e</t>
+          <t>https://www.indeed.com/viewjob?jk=933518dacc920f09</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Disaster Recovery Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Benchmark Solutions LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8cfebbb7e871628</t>
+          <t>https://www.indeed.com/viewjob?jk=eaeff5e1c81b908e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Benchmark Solutions LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1df3e0ee29922c</t>
+          <t>https://www.indeed.com/viewjob?jk=f8cfebbb7e871628</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark, Scala</t>
+          <t>IAM, RDS, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6fb94b58173aba</t>
+          <t>https://www.indeed.com/viewjob?jk=0f1df3e0ee29922c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management - East</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1f7dab55752b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6fb94b58173aba</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Senior Systems Engineer, UDS Data Management - East</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8317116e3b8b4</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1f7dab55752b3e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer - ML/AI Data Platform (Remote)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FEI Systems</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, Step Functions, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, SQS, SNS, RDS, Databricks</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58ce81b6255bf6b</t>
+          <t>https://www.indeed.com/viewjob?jk=b239490817bb3dba</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171403dbdac6e42f</t>
+          <t>https://www.indeed.com/viewjob?jk=50d8317116e3b8b4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Data Engineer - ML/AI Data Platform (Remote)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>FEI Systems</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Kinesis, Athena, Step Functions, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5378ca2d10086b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a58ce81b6255bf6b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI/ML Engineer (Hybrid)</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a2a750b8d45131</t>
+          <t>https://www.indeed.com/viewjob?jk=171403dbdac6e42f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Platform &amp; DevOps Engineer</t>
+          <t>AI/ML Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Azure, Spark, PySpark, Scala, Kafka, Polars</t>
+          <t>AWS, Glue, Athena, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,19 +951,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fc55dd920ed33e</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a2a750b8d45131</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist - Machine Learning</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd4b842829eab81b</t>
+          <t>https://www.indeed.com/viewjob?jk=d5378ca2d10086b6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Sr Platform &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, Azure, Spark, PySpark, Scala, Kafka, Polars</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d24c78be0131037</t>
+          <t>https://www.indeed.com/viewjob?jk=03fc55dd920ed33e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
+          <t>Data Scientist - Machine Learning</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Softengine</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=055c54c5a52e97d2</t>
+          <t>https://www.indeed.com/viewjob?jk=dd4b842829eab81b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e129ef424b7bb1</t>
+          <t>https://www.indeed.com/viewjob?jk=0d24c78be0131037</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kestra Financial</t>
+          <t>Softengine</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4aca5f146dc1fe</t>
+          <t>https://www.indeed.com/viewjob?jk=055c54c5a52e97d2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kestra Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6cbe9c6196981eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e129ef424b7bb1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kestra Financial</t>
+          <t>DNS Solutions Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9d37985c0bdcf2</t>
+          <t>https://www.indeed.com/viewjob?jk=7663c2a8691261bd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837e9f344d302e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=5a58cf7cc708c832</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DNS Solutions Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7663c2a8691261bd</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca8e86ee6ca254d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a58cf7cc708c832</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4aca5f146dc1fe</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca8e86ee6ca254d</t>
+          <t>https://www.indeed.com/viewjob?jk=c6cbe9c6196981eb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IT Specialist/Systems Administrator</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Customer Care First</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6d93d88b6a0a66</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9d37985c0bdcf2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9216704e953a3254</t>
+          <t>https://www.indeed.com/viewjob?jk=837e9f344d302e6d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer (AWS/Azure/GCP | Hybrid Cloud | AI Security)</t>
+          <t>IT Specialist/Systems Administrator</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LifeScale Analytics</t>
+          <t>Customer Care First</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Syracuse, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=187fb1dba54e59d2</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6d93d88b6a0a66</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Fully Remote!</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KinderCare Learning Companies</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b630719ad31d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=9216704e953a3254</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; Backend Platform Engineer</t>
+          <t>Senior Cloud Security Engineer (AWS/Azure/GCP | Hybrid Cloud | AI Security)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ASU Preparatory Academy</t>
+          <t>LifeScale Analytics</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,102 +1511,102 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c86711a678b9cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=187fb1dba54e59d2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Developer, IT Applications</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Storable</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Oracle, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb2c0deb86004e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8d616d744010b2d4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer - Management and Operations (Remote in US)</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>Development Infostructure</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, S3, API Gateway, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126895852cc1414c</t>
+          <t>https://www.indeed.com/viewjob?jk=49e5739e46621f5d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer - Fully Remote!</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>KinderCare Learning Companies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
+          <t>https://www.indeed.com/viewjob?jk=38b630719ad31d3a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Data Engineers</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,24 +1641,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, Hadoop, Hive, Spark</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=578e2464af530e79</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GCP ML Engineer (Vertex AI)</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce22f8b356b35619</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Cloud &amp; Backend Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>ASU Preparatory Academy</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8429c2a459d3de4f</t>
+          <t>https://www.indeed.com/viewjob?jk=4c86711a678b9cfb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NEXON America</t>
+          <t>Storable</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,42 +1746,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Splunk, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb2c0deb86004e8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
+          <t>GCP Cloud Engineer - Management and Operations (Remote in US)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>Resultant</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Santa Cruz, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e946f43c0ce5053</t>
+          <t>https://www.indeed.com/viewjob?jk=126895852cc1414c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer, Market Data New</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MIO Partners</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, RDS, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ce8c2bb2e05265</t>
+          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
+          <t>GCP ML Engineer (Vertex AI)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Santa Cruz, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,129 +1861,129 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
+          <t>https://www.indeed.com/viewjob?jk=ce22f8b356b35619</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Inspire11</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Dimensional Modeling</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcac04dbf474e01b</t>
+          <t>https://www.indeed.com/viewjob?jk=8429c2a459d3de4f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Product Owner II - BI (Memphis, TN or Remote in USA)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>St. Jude Children's Research Hospital</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44f16ef92378b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ea984ba020827de7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NEXON America</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2be041ba7dd258</t>
+          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Santa Cruz, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf763802f514ac89</t>
+          <t>https://www.indeed.com/viewjob?jk=1e946f43c0ce5053</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Santa Cruz, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7c3880bf1468af</t>
+          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad13b87eac68b71</t>
+          <t>https://www.indeed.com/viewjob?jk=cf763802f514ac89</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Front-End Growth Engineer</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EvaFi</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658e57cd8469a251</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7c3880bf1468af</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Market Data New</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>MIO Partners</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, RDS, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26d7493c6bd8679</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ce8c2bb2e05265</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Inspire11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Scala, Snowflake, MLOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c13da2a0f601ffa5</t>
+          <t>https://www.indeed.com/viewjob?jk=fcac04dbf474e01b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, API Gateway, Azure, Data Factory, Databricks, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,14 +2211,14 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44f16ef92378b0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4249a3228aea17d</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2be041ba7dd258</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer, Pro360 Product Group</t>
+          <t>Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Hadoop, Scala, SQL Server, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bc6c388f4a159c</t>
+          <t>https://www.indeed.com/viewjob?jk=c13da2a0f601ffa5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70cf81a93ee7ae14</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad13b87eac68b71</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Front-End Growth Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>EvaFi</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2af3b2ea12351135</t>
+          <t>https://www.indeed.com/viewjob?jk=658e57cd8469a251</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
+          <t>AWS, EMR, Lambda, API Gateway, Azure, Data Factory, Databricks, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55dd6036cf4386c2</t>
+          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
+          <t>https://www.indeed.com/viewjob?jk=b4249a3228aea17d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Data Engineer, Pro360 Product Group</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Hadoop, Scala, SQL Server, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=b0bc6c388f4a159c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sales/Solutions Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Artie</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c1fe1287b79994</t>
+          <t>https://www.indeed.com/viewjob?jk=70cf81a93ee7ae14</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Platform Architect - AI</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57c71c270f4f024f</t>
+          <t>https://www.indeed.com/viewjob?jk=2af3b2ea12351135</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f670c120137d065</t>
+          <t>https://www.indeed.com/viewjob?jk=55dd6036cf4386c2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Engineer Senior</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, ETL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5e0df0ff0f2609</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer III - UnderwritingCenter</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4f413a4cd84f6f</t>
+          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full stack</t>
+          <t>Sales/Solutions Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Artie</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,42 +2656,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a4c233ec9d2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=50c1fe1287b79994</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Platform Architect - AI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f52b7af2ce28a8</t>
+          <t>https://www.indeed.com/viewjob?jk=57c71c270f4f024f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer – Cloud and AI</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01f85e7d7e897954</t>
+          <t>https://www.indeed.com/viewjob?jk=4f670c120137d065</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>MuleSoft Integration Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bickham Services Unlimited, LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>API Gateway, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
+          <t>https://www.indeed.com/viewjob?jk=ff60d7a3553e89e2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>Engineer Senior</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, ETL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,94 +2806,94 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43fdee7cf569751d</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5e0df0ff0f2609</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer III - UnderwritingCenter</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Avature</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f0d7f99a5b402c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4f413a4cd84f6f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer 2 - Full stack</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, Flume, Spark, Scala, Kafka, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8925c0b6808e2ef8</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a4c233ec9d2bd</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Solution Architect with Presales Experience</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Avature</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,29 +2901,29 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43dbc51a5868e325</t>
+          <t>https://www.indeed.com/viewjob?jk=04f0d7f99a5b402c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Native Java Developer (U.S. remote)</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Railroad19</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, Scala, Oracle, MySQL, NoSQL, Jenkins</t>
+          <t>IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c864309c5f175c3e</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f52b7af2ce28a8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Engineer - Full Stack</t>
+          <t>Data Engineer – Cloud and AI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, CI/CD, Jenkins, GitHub Actions, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24fe9813b60c6c14</t>
+          <t>https://www.indeed.com/viewjob?jk=01f85e7d7e897954</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BeyondTrust</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e471f407b19da8</t>
+          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Teton Ridge</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9736ba6473e4804f</t>
+          <t>https://www.indeed.com/viewjob?jk=43fdee7cf569751d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Solution Architect with Presales Experience</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
+          <t>https://www.indeed.com/viewjob?jk=43dbc51a5868e325</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Developer (Systems Software) - TS/SCI w/ Polygraph</t>
+          <t>Cloud Native Java Developer (U.S. remote)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Railroad19</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Scala, ETL, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, Scala, Oracle, MySQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b918f48362f41a28</t>
+          <t>https://www.indeed.com/viewjob?jk=c864309c5f175c3e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d09fe840e33b4c7</t>
+          <t>https://www.indeed.com/viewjob?jk=fae30530e8043b01</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Remote / Project-Based Data Engineer for Public-Sector Data Modernization, Dashboards, and AI-Ready</t>
+          <t>Senior Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, PostgreSQL, MySQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, NoSQL, CI/CD, Jenkins, GitHub Actions, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f000f4be342c4377</t>
+          <t>https://www.indeed.com/viewjob?jk=24fe9813b60c6c14</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Serenity Healthcare</t>
+          <t>BeyondTrust</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fffc235cb241e45</t>
+          <t>https://www.indeed.com/viewjob?jk=12e471f407b19da8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Teton Ridge</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f39f88a9b70f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=9736ba6473e4804f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ec2088a10dc04e</t>
+          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Software Developer (Systems Software) - TS/SCI w/ Polygraph</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+          <t>AWS, RDS, Hadoop, Hive, Scala, ETL, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f2031edb48e342e</t>
+          <t>https://www.indeed.com/viewjob?jk=b918f48362f41a28</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>OJUSLLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc46a93049506224</t>
+          <t>https://www.indeed.com/viewjob?jk=8d09fe840e33b4c7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc004557d9736a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=e56229e27f5c6fd1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - ADF &amp; Databricks</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, Dimensional Modeling, ETL</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f3a914de107c82</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f39f88a9b70f0a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Oracle, PostgreSQL, MongoDB, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=490033b77e24b17c</t>
+          <t>https://www.indeed.com/viewjob?jk=1c41862eb239f163</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Remote / Project-Based Data Engineer for Public-Sector Data Modernization, Dashboards, and AI-Ready</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, PostgreSQL, MySQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56229e27f5c6fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=f000f4be342c4377</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Serenity Healthcare</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Oracle, PostgreSQL, MongoDB, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c41862eb239f163</t>
+          <t>https://www.indeed.com/viewjob?jk=9fffc235cb241e45</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Babylon, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d3d24d3399d0363</t>
+          <t>https://www.indeed.com/viewjob?jk=29ec2088a10dc04e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Power BI, Git, Python, SQL</t>
+          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9af17a3ab15e53</t>
+          <t>https://www.indeed.com/viewjob?jk=0f2031edb48e342e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SmartAdvocate</t>
+          <t>OJUSLLC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Jenkins</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=001c431f02e0a7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=fc46a93049506224</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Developer – Intelligent Systems &amp; Integrations</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5727dfe812017a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=dc004557d9736a0f</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Scientist &amp; Modeler</t>
+          <t>Senior Software Engineer, Global Banking &amp; Markets, Securities Settlement Engineering</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Iberdrola Group</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Orange, CT, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, GCP, Scala, PostgreSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39fab587fb046739</t>
+          <t>https://www.indeed.com/viewjob?jk=afcab31fabe71ed5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Development Infostructure</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, MLOps, CI/CD, Jenkins, Maven, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ba35ddf0464dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=15b8228527caa95f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Vidoori</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Hyattsville, MD, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff9c5f258d04aaa</t>
+          <t>https://www.indeed.com/viewjob?jk=7710e703cc72f4b0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Product Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Babylon, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410c7062135208be</t>
+          <t>https://www.indeed.com/viewjob?jk=3d3d24d3399d0363</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Scientist (944)</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ABC Supply Co., Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,15 +3846,190 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Power BI, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc9af17a3ab15e53</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AI DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SmartAdvocate</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Melville, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=001c431f02e0a7d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Software Developer – Intelligent Systems &amp; Integrations</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5727dfe812017a7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist &amp; Modeler</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Iberdrola Group</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Orange, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39fab587fb046739</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, ECS, Azure, MLOps, CI/CD, Jenkins, Maven, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1ba35ddf0464dd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Data Scientist (944)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ABC Supply Co., Inc.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>RDS, Azure, Databricks, ETL, ELT, Tableau, MLOps, MLflow, Git, Python</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a2beae7f9c463995</t>
         </is>

--- a/results/job_matches_2026-05-12.xlsx
+++ b/results/job_matches_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Expert AI &amp; Cloud Development Architect - Office of the CTO</t>
+          <t>Senior Engineer - Payments Modernization</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, API Gateway, IAM, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc8674d85a442c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f7aa9808e3bc85</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Engineer - Payments Modernization</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Oregon State University</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Corvallis, OR, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f7aa9808e3bc85</t>
+          <t>https://www.indeed.com/viewjob?jk=933518dacc920f09</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Senior Cloud Disaster Recovery Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Oregon State University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Corvallis, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933518dacc920f09</t>
+          <t>https://www.indeed.com/viewjob?jk=eaeff5e1c81b908e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Benchmark Solutions LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaeff5e1c81b908e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8cfebbb7e871628</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Benchmark Solutions LLC</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, DynamoDB</t>
+          <t>IAM, RDS, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8cfebbb7e871628</t>
+          <t>https://www.indeed.com/viewjob?jk=0f1df3e0ee29922c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1df3e0ee29922c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6fb94b58173aba</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Systems Engineer, UDS Data Management - East</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6fb94b58173aba</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1f7dab55752b3e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management - East</t>
+          <t>Software Engineer III- Python, PySpark, ETL, AWS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1f7dab55752b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=1e01551f023130f4</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI/ML Engineer (Hybrid)</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a2a750b8d45131</t>
+          <t>https://www.indeed.com/viewjob?jk=d5378ca2d10086b6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>AI/ML Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Athena, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5378ca2d10086b6</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a2a750b8d45131</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DNS Solutions Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7663c2a8691261bd</t>
+          <t>https://www.indeed.com/viewjob?jk=110879d3c05b187b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a58cf7cc708c832</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa4c8179a8ac4da</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca8e86ee6ca254d</t>
+          <t>https://www.indeed.com/viewjob?jk=f66f1fbb6c8a1a3b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kestra Financial</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4aca5f146dc1fe</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc984a42640329e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kestra Financial</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6cbe9c6196981eb</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfdcd1adce614e6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kestra Financial</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9d37985c0bdcf2</t>
+          <t>https://www.indeed.com/viewjob?jk=bd3763e7b5c9b674</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837e9f344d302e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb6a218ca916697</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IT Specialist/Systems Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Customer Care First</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6d93d88b6a0a66</t>
+          <t>https://www.indeed.com/viewjob?jk=d791e762f6d81f87</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9216704e953a3254</t>
+          <t>https://www.indeed.com/viewjob?jk=7943d064127358c8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer (AWS/Azure/GCP | Hybrid Cloud | AI Security)</t>
+          <t>Software Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LifeScale Analytics</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=187fb1dba54e59d2</t>
+          <t>https://www.indeed.com/viewjob?jk=14e64b70ed3febe9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Developer, IT Applications</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Encore Fire Protection</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Needham, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Oracle, Power BI, Jenkins</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, MySQL, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d616d744010b2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=f9585bb14bb3c50d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Development Infostructure</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, API Gateway, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e5739e46621f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=c4350b7356581efc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Fully Remote!</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>KinderCare Learning Companies</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b630719ad31d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4aca5f146dc1fe</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineers</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=578e2464af530e79</t>
+          <t>https://www.indeed.com/viewjob?jk=c6cbe9c6196981eb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, Hadoop, Hive, Spark</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9d37985c0bdcf2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; Backend Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ASU Preparatory Academy</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c86711a678b9cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=837e9f344d302e6d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Storable</t>
+          <t>DNS Solutions Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb2c0deb86004e8</t>
+          <t>https://www.indeed.com/viewjob?jk=7663c2a8691261bd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer - Management and Operations (Remote in US)</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126895852cc1414c</t>
+          <t>https://www.indeed.com/viewjob?jk=5a58cf7cc708c832</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,172 +1826,172 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca8e86ee6ca254d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GCP ML Engineer (Vertex AI)</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Development Infostructure</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Spark</t>
+          <t>AWS, Redshift, S3, API Gateway, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce22f8b356b35619</t>
+          <t>https://www.indeed.com/viewjob?jk=49e5739e46621f5d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8429c2a459d3de4f</t>
+          <t>https://www.indeed.com/viewjob?jk=9216704e953a3254</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Product Owner II - BI (Memphis, TN or Remote in USA)</t>
+          <t>Senior Cloud Security Engineer (AWS/Azure/GCP | Hybrid Cloud | AI Security)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>LifeScale Analytics</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea984ba020827de7</t>
+          <t>https://www.indeed.com/viewjob?jk=187fb1dba54e59d2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Machine Learning Engineer - Fully Remote!</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NEXON America</t>
+          <t>KinderCare Learning Companies</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Splunk, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
+          <t>https://www.indeed.com/viewjob?jk=38b630719ad31d3a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
+          <t>Senior Cloud &amp; Backend Platform Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>ASU Preparatory Academy</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Santa Cruz, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e946f43c0ce5053</t>
+          <t>https://www.indeed.com/viewjob?jk=4c86711a678b9cfb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>Storable</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Santa Cruz, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb2c0deb86004e8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>GCP Cloud Engineer - Management and Operations (Remote in US)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Resultant</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf763802f514ac89</t>
+          <t>https://www.indeed.com/viewjob?jk=126895852cc1414c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7c3880bf1468af</t>
+          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer, Market Data New</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MIO Partners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, RDS, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ce8c2bb2e05265</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP ML Engineer (Vertex AI)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Inspire11</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,164 +2176,164 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcac04dbf474e01b</t>
+          <t>https://www.indeed.com/viewjob?jk=ce22f8b356b35619</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Data Engineers</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44f16ef92378b0</t>
+          <t>https://www.indeed.com/viewjob?jk=578e2464af530e79</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NEXON America</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2be041ba7dd258</t>
+          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Scala, Snowflake, MLOps</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c13da2a0f601ffa5</t>
+          <t>https://www.indeed.com/viewjob?jk=8429c2a459d3de4f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Product Owner II - BI (Memphis, TN or Remote in USA)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>St. Jude Children's Research Hospital</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad13b87eac68b71</t>
+          <t>https://www.indeed.com/viewjob?jk=ea984ba020827de7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Front-End Growth Engineer</t>
+          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EvaFi</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Santa Cruz, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658e57cd8469a251</t>
+          <t>https://www.indeed.com/viewjob?jk=1e946f43c0ce5053</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Data Engineer, Market Data New</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MIO Partners</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, API Gateway, Azure, Data Factory, Databricks, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, RDS, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ce8c2bb2e05265</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Santa Cruz, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4249a3228aea17d</t>
+          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer, Pro360 Product Group</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Inspire11</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Hadoop, Scala, SQL Server, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bc6c388f4a159c</t>
+          <t>https://www.indeed.com/viewjob?jk=fcac04dbf474e01b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70cf81a93ee7ae14</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44f16ef92378b0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2af3b2ea12351135</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2be041ba7dd258</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55dd6036cf4386c2</t>
+          <t>https://www.indeed.com/viewjob?jk=cf763802f514ac89</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2582,11 +2582,11 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7c3880bf1468af</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Front-End Growth Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>EvaFi</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=658e57cd8469a251</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sales/Solutions Engineer</t>
+          <t>Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Artie</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c1fe1287b79994</t>
+          <t>https://www.indeed.com/viewjob?jk=c13da2a0f601ffa5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Platform Architect - AI</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, EMR, Lambda, API Gateway, Azure, Data Factory, Databricks, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57c71c270f4f024f</t>
+          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f670c120137d065</t>
+          <t>https://www.indeed.com/viewjob?jk=b4249a3228aea17d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MuleSoft Integration Developer</t>
+          <t>Data Engineer, Pro360 Product Group</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bickham Services Unlimited, LLC</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Hadoop, Scala, SQL Server, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,14 +2771,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff60d7a3553e89e2</t>
+          <t>https://www.indeed.com/viewjob?jk=b0bc6c388f4a159c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineer Senior</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, ETL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5e0df0ff0f2609</t>
+          <t>https://www.indeed.com/viewjob?jk=70cf81a93ee7ae14</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer III - UnderwritingCenter</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4f413a4cd84f6f</t>
+          <t>https://www.indeed.com/viewjob?jk=2af3b2ea12351135</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full stack</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,77 +2866,77 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a4c233ec9d2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=55dd6036cf4386c2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Avature</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f0d7f99a5b402c</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f52b7af2ce28a8</t>
+          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer – Cloud and AI</t>
+          <t>Software Engineer III - UnderwritingCenter</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01f85e7d7e897954</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4f413a4cd84f6f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Engineer Senior</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, ETL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5e0df0ff0f2609</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>Sales/Solutions Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>Artie</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43fdee7cf569751d</t>
+          <t>https://www.indeed.com/viewjob?jk=50c1fe1287b79994</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Solution Architect with Presales Experience</t>
+          <t>Platform Architect - AI</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43dbc51a5868e325</t>
+          <t>https://www.indeed.com/viewjob?jk=57c71c270f4f024f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud Native Java Developer (U.S. remote)</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Railroad19</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,29 +3111,29 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, Scala, Oracle, MySQL, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c864309c5f175c3e</t>
+          <t>https://www.indeed.com/viewjob?jk=c208f65820392c92</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae30530e8043b01</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f52b7af2ce28a8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Engineer - Full Stack</t>
+          <t>Data Engineer – Cloud and AI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, CI/CD, Jenkins, GitHub Actions, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24fe9813b60c6c14</t>
+          <t>https://www.indeed.com/viewjob?jk=01f85e7d7e897954</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BeyondTrust</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e471f407b19da8</t>
+          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Teton Ridge</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9736ba6473e4804f</t>
+          <t>https://www.indeed.com/viewjob?jk=43fdee7cf569751d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
+          <t>https://www.indeed.com/viewjob?jk=48a7dc9b2a0c6b63</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Developer (Systems Software) - TS/SCI w/ Polygraph</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Avature</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,42 +3321,42 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Scala, ETL, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b918f48362f41a28</t>
+          <t>https://www.indeed.com/viewjob?jk=04f0d7f99a5b402c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SilverEdge Government Solutions</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, ECS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,67 +3366,67 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d09fe840e33b4c7</t>
+          <t>https://www.indeed.com/viewjob?jk=8db426b190d5761e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Denovo Ventures</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Louisville, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56229e27f5c6fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=83484ce8e2c739af</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Senior Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, NoSQL, CI/CD, Jenkins, GitHub Actions, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f39f88a9b70f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=24fe9813b60c6c14</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>BeyondTrust</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Oracle, PostgreSQL, MongoDB, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c41862eb239f163</t>
+          <t>https://www.indeed.com/viewjob?jk=12e471f407b19da8</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Remote / Project-Based Data Engineer for Public-Sector Data Modernization, Dashboards, and AI-Ready</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Teton Ridge</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, PostgreSQL, MySQL, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f000f4be342c4377</t>
+          <t>https://www.indeed.com/viewjob?jk=9736ba6473e4804f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer (Systems Software) - TS/SCI w/ Polygraph</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Serenity Healthcare</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Hadoop, Hive, Scala, ETL, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fffc235cb241e45</t>
+          <t>https://www.indeed.com/viewjob?jk=b918f48362f41a28</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ec2088a10dc04e</t>
+          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f2031edb48e342e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d09fe840e33b4c7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Remote / Project-Based Data Engineer for Public-Sector Data Modernization, Dashboards, and AI-Ready</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>OJUSLLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, PostgreSQL, MySQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc46a93049506224</t>
+          <t>https://www.indeed.com/viewjob?jk=f000f4be342c4377</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Serenity Healthcare</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc004557d9736a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=9fffc235cb241e45</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Global Banking &amp; Markets, Securities Settlement Engineering</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, GCP, Scala, PostgreSQL, CI/CD, Docker, Git</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afcab31fabe71ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f39f88a9b70f0a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Development Infostructure</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15b8228527caa95f</t>
+          <t>https://www.indeed.com/viewjob?jk=29ec2088a10dc04e</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Vidoori</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hyattsville, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7710e703cc72f4b0</t>
+          <t>https://www.indeed.com/viewjob?jk=0f2031edb48e342e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>OJUSLLC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Babylon, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d3d24d3399d0363</t>
+          <t>https://www.indeed.com/viewjob?jk=fc46a93049506224</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Power BI, Git, Python, SQL</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9af17a3ab15e53</t>
+          <t>https://www.indeed.com/viewjob?jk=48debf03335c270f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SmartAdvocate</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Jenkins</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=001c431f02e0a7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e56229e27f5c6fd1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Developer – Intelligent Systems &amp; Integrations</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>Oracle, PostgreSQL, MongoDB, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5727dfe812017a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=1c41862eb239f163</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Scientist &amp; Modeler</t>
+          <t>Software Engineer III - Java, Springboot</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Iberdrola Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Orange, CT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39fab587fb046739</t>
+          <t>https://www.indeed.com/viewjob?jk=8cb68eebaeaaf747</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vidoori</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hyattsville, MD, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, MLOps, CI/CD, Jenkins, Maven, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ba35ddf0464dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=7710e703cc72f4b0</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Scientist (944)</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ABC Supply Co., Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,15 +4021,190 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Power BI, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc9af17a3ab15e53</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Product Software Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Wolters Kluwer</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Babylon, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d3d24d3399d0363</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AI DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SmartAdvocate</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Melville, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=001c431f02e0a7d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Software Developer – Intelligent Systems &amp; Integrations</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5727dfe812017a7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist &amp; Modeler</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Iberdrola Group</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Orange, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39fab587fb046739</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Data Scientist (944)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ABC Supply Co., Inc.</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
           <t>RDS, Azure, Databricks, ETL, ELT, Tableau, MLOps, MLflow, Git, Python</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a2beae7f9c463995</t>
         </is>

--- a/results/job_matches_2026-05-12.xlsx
+++ b/results/job_matches_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Engineer - Payments Modernization</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Oregon State University</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Corvallis, OR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f7aa9808e3bc85</t>
+          <t>https://www.indeed.com/viewjob?jk=933518dacc920f09</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Senior Cloud Disaster Recovery Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Oregon State University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Corvallis, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933518dacc920f09</t>
+          <t>https://www.indeed.com/viewjob?jk=eaeff5e1c81b908e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Benchmark Solutions LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaeff5e1c81b908e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8cfebbb7e871628</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Benchmark Solutions LLC</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, DynamoDB</t>
+          <t>IAM, RDS, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8cfebbb7e871628</t>
+          <t>https://www.indeed.com/viewjob?jk=0f1df3e0ee29922c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1df3e0ee29922c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6fb94b58173aba</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Systems Engineer, UDS Data Management - East</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6fb94b58173aba</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1f7dab55752b3e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management - East</t>
+          <t>Software Engineer III- Python, PySpark, ETL, AWS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1f7dab55752b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=1e01551f023130f4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, PySpark, ETL, AWS</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,69 +766,69 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, SQS, SNS, RDS, Databricks</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e01551f023130f4</t>
+          <t>https://www.indeed.com/viewjob?jk=b239490817bb3dba</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, SQS, SNS, RDS, Databricks</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b239490817bb3dba</t>
+          <t>https://www.indeed.com/viewjob?jk=50d8317116e3b8b4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Data Engineer - ML/AI Data Platform (Remote)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>FEI Systems</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, Glue, Kinesis, Athena, Step Functions, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8317116e3b8b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a58ce81b6255bf6b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - ML/AI Data Platform (Remote)</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FEI Systems</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, Step Functions, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58ce81b6255bf6b</t>
+          <t>https://www.indeed.com/viewjob?jk=171403dbdac6e42f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>AI/ML Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Athena, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171403dbdac6e42f</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a2a750b8d45131</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI/ML Engineer (Hybrid)</t>
+          <t>Sr Platform &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, Azure, Spark, PySpark, Scala, Kafka, Polars</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a2a750b8d45131</t>
+          <t>https://www.indeed.com/viewjob?jk=03fc55dd920ed33e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Platform &amp; DevOps Engineer</t>
+          <t>Data Scientist - Machine Learning</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Azure, Spark, PySpark, Scala, Kafka, Polars</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fc55dd920ed33e</t>
+          <t>https://www.indeed.com/viewjob?jk=dd4b842829eab81b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist - Machine Learning</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow</t>
+          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd4b842829eab81b</t>
+          <t>https://www.indeed.com/viewjob?jk=0d24c78be0131037</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Softengine</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d24c78be0131037</t>
+          <t>https://www.indeed.com/viewjob?jk=055c54c5a52e97d2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Softengine</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=055c54c5a52e97d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e129ef424b7bb1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Encore Fire Protection</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Needham, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, MySQL, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e129ef424b7bb1</t>
+          <t>https://www.indeed.com/viewjob?jk=f9585bb14bb3c50d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110879d3c05b187b</t>
+          <t>https://www.indeed.com/viewjob?jk=c4350b7356581efc</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>DNS Solutions Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa4c8179a8ac4da</t>
+          <t>https://www.indeed.com/viewjob?jk=7663c2a8691261bd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66f1fbb6c8a1a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=5a58cf7cc708c832</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc984a42640329e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca8e86ee6ca254d</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfdcd1adce614e6</t>
+          <t>https://www.indeed.com/viewjob?jk=110879d3c05b187b</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd3763e7b5c9b674</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa4c8179a8ac4da</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb6a218ca916697</t>
+          <t>https://www.indeed.com/viewjob?jk=f66f1fbb6c8a1a3b</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d791e762f6d81f87</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc984a42640329e</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7943d064127358c8</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfdcd1adce614e6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e64b70ed3febe9</t>
+          <t>https://www.indeed.com/viewjob?jk=bd3763e7b5c9b674</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Encore Fire Protection</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Needham, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, MySQL, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9585bb14bb3c50d</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb6a218ca916697</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4350b7356581efc</t>
+          <t>https://www.indeed.com/viewjob?jk=d791e762f6d81f87</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kestra Financial</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4aca5f146dc1fe</t>
+          <t>https://www.indeed.com/viewjob?jk=7943d064127358c8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Software Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kestra Financial</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6cbe9c6196981eb</t>
+          <t>https://www.indeed.com/viewjob?jk=14e64b70ed3febe9</t>
         </is>
       </c>
     </row>
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9d37985c0bdcf2</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4aca5f146dc1fe</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837e9f344d302e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=c6cbe9c6196981eb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DNS Solutions Inc.</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, NoSQL, ETL</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7663c2a8691261bd</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9d37985c0bdcf2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a58cf7cc708c832</t>
+          <t>https://www.indeed.com/viewjob?jk=837e9f344d302e6d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Senior Cloud Security Engineer (AWS/Azure/GCP | Hybrid Cloud | AI Security)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LifeScale Analytics</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Glue, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca8e86ee6ca254d</t>
+          <t>https://www.indeed.com/viewjob?jk=187fb1dba54e59d2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Senior Machine Learning Engineer - Fully Remote!</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Development Infostructure</t>
+          <t>KinderCare Learning Companies</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, API Gateway, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e5739e46621f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=38b630719ad31d3a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Development Infostructure</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, S3, API Gateway, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9216704e953a3254</t>
+          <t>https://www.indeed.com/viewjob?jk=49e5739e46621f5d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer (AWS/Azure/GCP | Hybrid Cloud | AI Security)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LifeScale Analytics</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,59 +1931,59 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=187fb1dba54e59d2</t>
+          <t>https://www.indeed.com/viewjob?jk=9216704e953a3254</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Fully Remote!</t>
+          <t>Data Engineers</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>KinderCare Learning Companies</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b630719ad31d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=578e2464af530e79</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; Backend Platform Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ASU Preparatory Academy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c86711a678b9cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Cloud &amp; Backend Platform Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Storable</t>
+          <t>ASU Preparatory Academy</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb2c0deb86004e8</t>
+          <t>https://www.indeed.com/viewjob?jk=4c86711a678b9cfb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer - Management and Operations (Remote in US)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>Storable</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126895852cc1414c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb2c0deb86004e8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Cloud Engineer - Management and Operations (Remote in US)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Resultant</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
+          <t>https://www.indeed.com/viewjob?jk=126895852cc1414c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, Hadoop, Hive, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineers</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>NEXON America</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=578e2464af530e79</t>
+          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Product Owner II - BI (Memphis, TN or Remote in USA)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NEXON America</t>
+          <t>St. Jude Children's Research Hospital</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Splunk, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
+          <t>https://www.indeed.com/viewjob?jk=ea984ba020827de7</t>
         </is>
       </c>
     </row>
@@ -2288,35 +2288,35 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Product Owner II - BI (Memphis, TN or Remote in USA)</t>
+          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Santa Cruz, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea984ba020827de7</t>
+          <t>https://www.indeed.com/viewjob?jk=1e946f43c0ce5053</t>
         </is>
       </c>
     </row>
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e946f43c0ce5053</t>
+          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer, Market Data New</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MIO Partners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, RDS, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ce8c2bb2e05265</t>
+          <t>https://www.indeed.com/viewjob?jk=cf763802f514ac89</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Santa Cruz, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7c3880bf1468af</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Market Data New</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Inspire11</t>
+          <t>MIO Partners</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, RDS, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcac04dbf474e01b</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ce8c2bb2e05265</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Inspire11</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44f16ef92378b0</t>
+          <t>https://www.indeed.com/viewjob?jk=fcac04dbf474e01b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2be041ba7dd258</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44f16ef92378b0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf763802f514ac89</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2be041ba7dd258</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Front-End Growth Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EvaFi</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7c3880bf1468af</t>
+          <t>https://www.indeed.com/viewjob?jk=658e57cd8469a251</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Front-End Growth Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EvaFi</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, API Gateway, Azure, Data Factory, Databricks, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658e57cd8469a251</t>
+          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Scala, Snowflake, MLOps</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c13da2a0f601ffa5</t>
+          <t>https://www.indeed.com/viewjob?jk=b4249a3228aea17d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Data Engineer, Pro360 Product Group</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, API Gateway, Azure, Data Factory, Databricks, Scala, ETL, ELT</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Hadoop, Scala, SQL Server, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
+          <t>https://www.indeed.com/viewjob?jk=b0bc6c388f4a159c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4249a3228aea17d</t>
+          <t>https://www.indeed.com/viewjob?jk=70cf81a93ee7ae14</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer, Pro360 Product Group</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Hadoop, Scala, SQL Server, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bc6c388f4a159c</t>
+          <t>https://www.indeed.com/viewjob?jk=2af3b2ea12351135</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70cf81a93ee7ae14</t>
+          <t>https://www.indeed.com/viewjob?jk=55dd6036cf4386c2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2af3b2ea12351135</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55dd6036cf4386c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7bac5379b2ecd01c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Software Engineer III - UnderwritingCenter</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4f413a4cd84f6f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Engineer Senior</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, ETL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5e0df0ff0f2609</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer III - UnderwritingCenter</t>
+          <t>Sales/Solutions Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Artie</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4f413a4cd84f6f</t>
+          <t>https://www.indeed.com/viewjob?jk=50c1fe1287b79994</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Engineer Senior</t>
+          <t>Platform Architect - AI</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, ETL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,67 +3016,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5e0df0ff0f2609</t>
+          <t>https://www.indeed.com/viewjob?jk=57c71c270f4f024f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sales/Solutions Engineer</t>
+          <t>Senior Data Engineer - Informatica IDMC &amp; CDGC (Data Lineage &amp; Data Quality)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Artie</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Redshift, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c1fe1287b79994</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6fa1054166d69d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Platform Architect - AI</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57c71c270f4f024f</t>
+          <t>https://www.indeed.com/viewjob?jk=48a7dc9b2a0c6b63</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Avature</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c208f65820392c92</t>
+          <t>https://www.indeed.com/viewjob?jk=04f0d7f99a5b402c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f52b7af2ce28a8</t>
+          <t>https://www.indeed.com/viewjob?jk=c208f65820392c92</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer – Cloud and AI</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01f85e7d7e897954</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f52b7af2ce28a8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Data Engineer – Cloud and AI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
+          <t>https://www.indeed.com/viewjob?jk=01f85e7d7e897954</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43fdee7cf569751d</t>
+          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>SilverEdge Government Solutions</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, ECS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a7dc9b2a0c6b63</t>
+          <t>https://www.indeed.com/viewjob?jk=8db426b190d5761e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Avature</t>
+          <t>Denovo Ventures</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Louisville, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f0d7f99a5b402c</t>
+          <t>https://www.indeed.com/viewjob?jk=83484ce8e2c739af</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SilverEdge Government Solutions</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, NoSQL, CI/CD, Jenkins, GitHub Actions, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db426b190d5761e</t>
+          <t>https://www.indeed.com/viewjob?jk=24fe9813b60c6c14</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Denovo Ventures</t>
+          <t>BeyondTrust</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Louisville, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83484ce8e2c739af</t>
+          <t>https://www.indeed.com/viewjob?jk=12e471f407b19da8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Engineer - Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>Teton Ridge</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, CI/CD, Jenkins, GitHub Actions, Maven, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24fe9813b60c6c14</t>
+          <t>https://www.indeed.com/viewjob?jk=9736ba6473e4804f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BeyondTrust</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e471f407b19da8</t>
+          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Developer (Systems Software) - TS/SCI w/ Polygraph</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Teton Ridge</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Hive, Scala, ETL, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9736ba6473e4804f</t>
+          <t>https://www.indeed.com/viewjob?jk=b918f48362f41a28</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Developer (Systems Software) - TS/SCI w/ Polygraph</t>
+          <t>DevOps Engineer- Ashburn, VA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Ellumen, Inc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Scala, ETL, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,59 +3541,59 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b918f48362f41a28</t>
+          <t>https://www.indeed.com/viewjob?jk=797eb835c7f60f42</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Senior Data Engineer - Informatica IDMC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Git</t>
+          <t>AWS, Redshift, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfba15617362e81</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d09fe840e33b4c7</t>
+          <t>https://www.indeed.com/viewjob?jk=48debf03335c270f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Remote / Project-Based Data Engineer for Public-Sector Data Modernization, Dashboards, and AI-Ready</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, PostgreSQL, MySQL, ETL, ELT, Power BI</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f000f4be342c4377</t>
+          <t>https://www.indeed.com/viewjob?jk=8d09fe840e33b4c7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Serenity Healthcare</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fffc235cb241e45</t>
+          <t>https://www.indeed.com/viewjob?jk=e56229e27f5c6fd1</t>
         </is>
       </c>
     </row>
@@ -3723,17 +3723,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+          <t>Oracle, PostgreSQL, MongoDB, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ec2088a10dc04e</t>
+          <t>https://www.indeed.com/viewjob?jk=1c41862eb239f163</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Remote / Project-Based Data Engineer for Public-Sector Data Modernization, Dashboards, and AI-Ready</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, PostgreSQL, MySQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f2031edb48e342e</t>
+          <t>https://www.indeed.com/viewjob?jk=f000f4be342c4377</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>OJUSLLC</t>
+          <t>Serenity Healthcare</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc46a93049506224</t>
+          <t>https://www.indeed.com/viewjob?jk=9fffc235cb241e45</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48debf03335c270f</t>
+          <t>https://www.indeed.com/viewjob?jk=29ec2088a10dc04e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56229e27f5c6fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=0f2031edb48e342e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>OJUSLLC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Oracle, PostgreSQL, MongoDB, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c41862eb239f163</t>
+          <t>https://www.indeed.com/viewjob?jk=fc46a93049506224</t>
         </is>
       </c>
     </row>
@@ -4178,17 +4178,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Scientist (944)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ABC Supply Co., Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,15 +4196,50 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Docker, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87e755ed281f268b</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Data Scientist (944)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ABC Supply Co., Inc.</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
           <t>RDS, Azure, Databricks, ETL, ELT, Tableau, MLOps, MLflow, Git, Python</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a2beae7f9c463995</t>
         </is>

--- a/results/job_matches_2026-05-12.xlsx
+++ b/results/job_matches_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,25 +958,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Platform &amp; DevOps Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Azure, Spark, PySpark, Scala, Kafka, Polars</t>
+          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fc55dd920ed33e</t>
+          <t>https://www.indeed.com/viewjob?jk=0d24c78be0131037</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist - Machine Learning</t>
+          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Softengine</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd4b842829eab81b</t>
+          <t>https://www.indeed.com/viewjob?jk=055c54c5a52e97d2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d24c78be0131037</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e129ef424b7bb1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Softengine</t>
+          <t>Encore Fire Protection</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>Needham, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, MySQL, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=055c54c5a52e97d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f9585bb14bb3c50d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e129ef424b7bb1</t>
+          <t>https://www.indeed.com/viewjob?jk=c4350b7356581efc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Encore Fire Protection</t>
+          <t>DNS Solutions Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Needham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, MySQL, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9585bb14bb3c50d</t>
+          <t>https://www.indeed.com/viewjob?jk=7663c2a8691261bd</t>
         </is>
       </c>
     </row>
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4350b7356581efc</t>
+          <t>https://www.indeed.com/viewjob?jk=5a58cf7cc708c832</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DNS Solutions Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7663c2a8691261bd</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca8e86ee6ca254d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a58cf7cc708c832</t>
+          <t>https://www.indeed.com/viewjob?jk=110879d3c05b187b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca8e86ee6ca254d</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa4c8179a8ac4da</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110879d3c05b187b</t>
+          <t>https://www.indeed.com/viewjob?jk=f66f1fbb6c8a1a3b</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa4c8179a8ac4da</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc984a42640329e</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66f1fbb6c8a1a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfdcd1adce614e6</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc984a42640329e</t>
+          <t>https://www.indeed.com/viewjob?jk=bd3763e7b5c9b674</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfdcd1adce614e6</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb6a218ca916697</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd3763e7b5c9b674</t>
+          <t>https://www.indeed.com/viewjob?jk=d791e762f6d81f87</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb6a218ca916697</t>
+          <t>https://www.indeed.com/viewjob?jk=7943d064127358c8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d791e762f6d81f87</t>
+          <t>https://www.indeed.com/viewjob?jk=14e64b70ed3febe9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7943d064127358c8</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4aca5f146dc1fe</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e64b70ed3febe9</t>
+          <t>https://www.indeed.com/viewjob?jk=c6cbe9c6196981eb</t>
         </is>
       </c>
     </row>
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4aca5f146dc1fe</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9d37985c0bdcf2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kestra Financial</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6cbe9c6196981eb</t>
+          <t>https://www.indeed.com/viewjob?jk=837e9f344d302e6d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Cloud Security Engineer (AWS/Azure/GCP | Hybrid Cloud | AI Security)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kestra Financial</t>
+          <t>LifeScale Analytics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Glue, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9d37985c0bdcf2</t>
+          <t>https://www.indeed.com/viewjob?jk=187fb1dba54e59d2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer - Fully Remote!</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>KinderCare Learning Companies</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837e9f344d302e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=38b630719ad31d3a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer (AWS/Azure/GCP | Hybrid Cloud | AI Security)</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LifeScale Analytics</t>
+          <t>Development Infostructure</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, CI/CD</t>
+          <t>AWS, Redshift, S3, API Gateway, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=187fb1dba54e59d2</t>
+          <t>https://www.indeed.com/viewjob?jk=49e5739e46621f5d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Fully Remote!</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KinderCare Learning Companies</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b630719ad31d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=9216704e953a3254</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Development Infostructure</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, API Gateway, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e5739e46621f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Cloud &amp; Backend Platform Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>ASU Preparatory Academy</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9216704e953a3254</t>
+          <t>https://www.indeed.com/viewjob?jk=4c86711a678b9cfb</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineers</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Storable</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=578e2464af530e79</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb2c0deb86004e8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>GCP Cloud Engineer - Management and Operations (Remote in US)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Resultant</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, Hadoop, Hive, Spark</t>
+          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=126895852cc1414c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; Backend Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ASU Preparatory Academy</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c86711a678b9cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>GCP ML Engineer (Vertex AI)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Storable</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb2c0deb86004e8</t>
+          <t>https://www.indeed.com/viewjob?jk=ce22f8b356b35619</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer - Management and Operations (Remote in US)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>NEXON America</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126895852cc1414c</t>
+          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Product Owner II - BI (Memphis, TN or Remote in USA)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>St. Jude Children's Research Hospital</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
+          <t>https://www.indeed.com/viewjob?jk=ea984ba020827de7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GCP ML Engineer (Vertex AI)</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,139 +2166,139 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Spark</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce22f8b356b35619</t>
+          <t>https://www.indeed.com/viewjob?jk=8429c2a459d3de4f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NEXON America</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Santa Cruz, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Splunk, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1e946f43c0ce5053</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Product Owner II - BI (Memphis, TN or Remote in USA)</t>
+          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Santa Cruz, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea984ba020827de7</t>
+          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8429c2a459d3de4f</t>
+          <t>https://www.indeed.com/viewjob?jk=cf763802f514ac89</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Santa Cruz, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e946f43c0ce5053</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7c3880bf1468af</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>Inspire11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Santa Cruz, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
+          <t>https://www.indeed.com/viewjob?jk=fcac04dbf474e01b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf763802f514ac89</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44f16ef92378b0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7c3880bf1468af</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2be041ba7dd258</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer, Market Data New</t>
+          <t>Front-End Growth Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MIO Partners</t>
+          <t>EvaFi</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, RDS, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ce8c2bb2e05265</t>
+          <t>https://www.indeed.com/viewjob?jk=658e57cd8469a251</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Inspire11</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, EMR, Lambda, API Gateway, Azure, Data Factory, Databricks, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcac04dbf474e01b</t>
+          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44f16ef92378b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b4249a3228aea17d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Data Engineer, Pro360 Product Group</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Hadoop, Scala, SQL Server, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2be041ba7dd258</t>
+          <t>https://www.indeed.com/viewjob?jk=b0bc6c388f4a159c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Front-End Growth Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EvaFi</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658e57cd8469a251</t>
+          <t>https://www.indeed.com/viewjob?jk=70cf81a93ee7ae14</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, API Gateway, Azure, Data Factory, Databricks, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
+          <t>https://www.indeed.com/viewjob?jk=2af3b2ea12351135</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4249a3228aea17d</t>
+          <t>https://www.indeed.com/viewjob?jk=55dd6036cf4386c2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer, Pro360 Product Group</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Hadoop, Scala, SQL Server, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bc6c388f4a159c</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Software Engineer III - UnderwritingCenter</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70cf81a93ee7ae14</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4f413a4cd84f6f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Engineer Senior</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, ETL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2af3b2ea12351135</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5e0df0ff0f2609</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sales/Solutions Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>Artie</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55dd6036cf4386c2</t>
+          <t>https://www.indeed.com/viewjob?jk=50c1fe1287b79994</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Platform Architect - AI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
+          <t>https://www.indeed.com/viewjob?jk=57c71c270f4f024f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer - Informatica IDMC &amp; CDGC (Data Lineage &amp; Data Quality)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, Airflow</t>
+          <t>AWS, Redshift, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bac5379b2ecd01c</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6fa1054166d69d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer III - UnderwritingCenter</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,102 +2911,102 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4f413a4cd84f6f</t>
+          <t>https://www.indeed.com/viewjob?jk=48a7dc9b2a0c6b63</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer Senior</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Avature</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, ETL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5e0df0ff0f2609</t>
+          <t>https://www.indeed.com/viewjob?jk=04f0d7f99a5b402c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sales/Solutions Engineer</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Artie</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c1fe1287b79994</t>
+          <t>https://www.indeed.com/viewjob?jk=c208f65820392c92</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Platform Architect - AI</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57c71c270f4f024f</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f52b7af2ce28a8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Informatica IDMC &amp; CDGC (Data Lineage &amp; Data Quality)</t>
+          <t>Data Engineer – Cloud and AI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6fa1054166d69d</t>
+          <t>https://www.indeed.com/viewjob?jk=01f85e7d7e897954</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a7dc9b2a0c6b63</t>
+          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Avature</t>
+          <t>Denovo Ventures</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Louisville, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f0d7f99a5b402c</t>
+          <t>https://www.indeed.com/viewjob?jk=83484ce8e2c739af</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Senior Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, NoSQL, CI/CD, Jenkins, GitHub Actions, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c208f65820392c92</t>
+          <t>https://www.indeed.com/viewjob?jk=24fe9813b60c6c14</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>BeyondTrust</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f52b7af2ce28a8</t>
+          <t>https://www.indeed.com/viewjob?jk=12e471f407b19da8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer – Cloud and AI</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01f85e7d7e897954</t>
+          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Software Developer (Systems Software) - TS/SCI w/ Polygraph</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Hadoop, Hive, Scala, ETL, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,102 +3261,102 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
+          <t>https://www.indeed.com/viewjob?jk=b918f48362f41a28</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Data Engineer - Informatica IDMC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SilverEdge Government Solutions</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db426b190d5761e</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfba15617362e81</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Denovo Ventures</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Louisville, CO, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83484ce8e2c739af</t>
+          <t>https://www.indeed.com/viewjob?jk=48debf03335c270f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Engineer - Full Stack</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, CI/CD, Jenkins, GitHub Actions, Maven, Docker, Kubernetes</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24fe9813b60c6c14</t>
+          <t>https://www.indeed.com/viewjob?jk=8d09fe840e33b4c7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BeyondTrust</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e471f407b19da8</t>
+          <t>https://www.indeed.com/viewjob?jk=e56229e27f5c6fd1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Teton Ridge</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9736ba6473e4804f</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f39f88a9b70f0a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Git</t>
+          <t>Oracle, PostgreSQL, MongoDB, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
+          <t>https://www.indeed.com/viewjob?jk=1c41862eb239f163</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Developer (Systems Software) - TS/SCI w/ Polygraph</t>
+          <t>Remote / Project-Based Data Engineer for Public-Sector Data Modernization, Dashboards, and AI-Ready</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Scala, ETL, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, PostgreSQL, MySQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b918f48362f41a28</t>
+          <t>https://www.indeed.com/viewjob?jk=f000f4be342c4377</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DevOps Engineer- Ashburn, VA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ellumen, Inc</t>
+          <t>Serenity Healthcare</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=797eb835c7f60f42</t>
+          <t>https://www.indeed.com/viewjob?jk=9fffc235cb241e45</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Informatica IDMC</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfba15617362e81</t>
+          <t>https://www.indeed.com/viewjob?jk=29ec2088a10dc04e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48debf03335c270f</t>
+          <t>https://www.indeed.com/viewjob?jk=0f2031edb48e342e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d09fe840e33b4c7</t>
+          <t>https://www.indeed.com/viewjob?jk=569983f090ab2e02</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Vidoori</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Hyattsville, MD, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,14 +3681,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56229e27f5c6fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=7710e703cc72f4b0</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f39f88a9b70f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9af17a3ab15e53</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Product Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Babylon, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oracle, PostgreSQL, MongoDB, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c41862eb239f163</t>
+          <t>https://www.indeed.com/viewjob?jk=3d3d24d3399d0363</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Remote / Project-Based Data Engineer for Public-Sector Data Modernization, Dashboards, and AI-Ready</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SmartAdvocate</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, PostgreSQL, MySQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f000f4be342c4377</t>
+          <t>https://www.indeed.com/viewjob?jk=001c431f02e0a7d6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist &amp; Modeler</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Serenity Healthcare</t>
+          <t>Iberdrola Group</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Orange, CT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fffc235cb241e45</t>
+          <t>https://www.indeed.com/viewjob?jk=39fab587fb046739</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Docker, Git, Datadog</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ec2088a10dc04e</t>
+          <t>https://www.indeed.com/viewjob?jk=87e755ed281f268b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Data Scientist (944)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ABC Supply Co., Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+          <t>RDS, Azure, Databricks, ETL, ELT, Tableau, MLOps, MLflow, Git, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3890,356 +3890,6 @@
         </is>
       </c>
       <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f2031edb48e342e</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Azure Data Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>OJUSLLC</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc46a93049506224</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Java, Springboot</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8cb68eebaeaaf747</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Vidoori</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Hyattsville, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7710e703cc72f4b0</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Azure Data Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Power BI, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9af17a3ab15e53</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Product Software Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Wolters Kluwer</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Babylon, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d3d24d3399d0363</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>AI DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>SmartAdvocate</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Melville, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=001c431f02e0a7d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Software Developer – Intelligent Systems &amp; Integrations</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>McKesson</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5727dfe812017a7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist &amp; Modeler</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Iberdrola Group</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Orange, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39fab587fb046739</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Glendale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Docker, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87e755ed281f268b</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Data Scientist (944)</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>ABC Supply Co., Inc.</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, ETL, ELT, Tableau, MLOps, MLflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a2beae7f9c463995</t>
         </is>

--- a/results/job_matches_2026-05-12.xlsx
+++ b/results/job_matches_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,87 +503,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Data Engineer - Optum Advisory Board - Remote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Oregon State University</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Corvallis, OR, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933518dacc920f09</t>
+          <t>https://www.indeed.com/viewjob?jk=dff403bb7c12a386</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Benchmark Solutions LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaeff5e1c81b908e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8cfebbb7e871628</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Benchmark Solutions LLC</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, DynamoDB</t>
+          <t>IAM, RDS, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8cfebbb7e871628</t>
+          <t>https://www.indeed.com/viewjob?jk=0f1df3e0ee29922c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1df3e0ee29922c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6fb94b58173aba</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Systems Engineer, UDS Data Management - East</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6fb94b58173aba</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1f7dab55752b3e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management - East</t>
+          <t>Software Engineer III- Python, PySpark, ETL, AWS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1f7dab55752b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=1e01551f023130f4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, PySpark, ETL, AWS</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,69 +731,69 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, SQS, SNS, RDS, Databricks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e01551f023130f4</t>
+          <t>https://www.indeed.com/viewjob?jk=b239490817bb3dba</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, SQS, SNS, RDS, Databricks</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b239490817bb3dba</t>
+          <t>https://www.indeed.com/viewjob?jk=50d8317116e3b8b4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8317116e3b8b4</t>
+          <t>https://www.indeed.com/viewjob?jk=171403dbdac6e42f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer - ML/AI Data Platform (Remote)</t>
+          <t>AI/ML Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FEI Systems</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, Step Functions, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Athena, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58ce81b6255bf6b</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a2a750b8d45131</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171403dbdac6e42f</t>
+          <t>https://www.indeed.com/viewjob?jk=d5378ca2d10086b6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI/ML Engineer (Hybrid)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake</t>
+          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a2a750b8d45131</t>
+          <t>https://www.indeed.com/viewjob?jk=0d24c78be0131037</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Encore Fire Protection</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Needham, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, MySQL, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5378ca2d10086b6</t>
+          <t>https://www.indeed.com/viewjob?jk=f9585bb14bb3c50d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,94 +986,94 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d24c78be0131037</t>
+          <t>https://www.indeed.com/viewjob?jk=c4350b7356581efc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Softengine</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=055c54c5a52e97d2</t>
+          <t>https://www.indeed.com/viewjob?jk=110879d3c05b187b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e129ef424b7bb1</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa4c8179a8ac4da</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Encore Fire Protection</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Needham, MA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, MySQL, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9585bb14bb3c50d</t>
+          <t>https://www.indeed.com/viewjob?jk=f66f1fbb6c8a1a3b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4350b7356581efc</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc984a42640329e</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DNS Solutions Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7663c2a8691261bd</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfdcd1adce614e6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a58cf7cc708c832</t>
+          <t>https://www.indeed.com/viewjob?jk=bd3763e7b5c9b674</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca8e86ee6ca254d</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb6a218ca916697</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110879d3c05b187b</t>
+          <t>https://www.indeed.com/viewjob?jk=d791e762f6d81f87</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa4c8179a8ac4da</t>
+          <t>https://www.indeed.com/viewjob?jk=7943d064127358c8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66f1fbb6c8a1a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=14e64b70ed3febe9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc984a42640329e</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4aca5f146dc1fe</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfdcd1adce614e6</t>
+          <t>https://www.indeed.com/viewjob?jk=c6cbe9c6196981eb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd3763e7b5c9b674</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9d37985c0bdcf2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb6a218ca916697</t>
+          <t>https://www.indeed.com/viewjob?jk=837e9f344d302e6d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Development Infostructure</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Redshift, S3, API Gateway, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d791e762f6d81f87</t>
+          <t>https://www.indeed.com/viewjob?jk=49e5739e46621f5d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7943d064127358c8</t>
+          <t>https://www.indeed.com/viewjob?jk=9216704e953a3254</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML</t>
+          <t>Senior Cloud Security Engineer (AWS/Azure/GCP | Hybrid Cloud | AI Security)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>LifeScale Analytics</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Glue, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e64b70ed3febe9</t>
+          <t>https://www.indeed.com/viewjob?jk=187fb1dba54e59d2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Machine Learning Engineer - Fully Remote!</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kestra Financial</t>
+          <t>KinderCare Learning Companies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,102 +1616,102 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4aca5f146dc1fe</t>
+          <t>https://www.indeed.com/viewjob?jk=38b630719ad31d3a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kestra Financial</t>
+          <t>Fuse Fundraising</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6cbe9c6196981eb</t>
+          <t>https://www.indeed.com/viewjob?jk=af281bb5ea90fb04</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>GCP Cloud Engineer - Management and Operations (Remote in US)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kestra Financial</t>
+          <t>Resultant</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9d37985c0bdcf2</t>
+          <t>https://www.indeed.com/viewjob?jk=126895852cc1414c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud &amp; Backend Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>ASU Preparatory Academy</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837e9f344d302e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=4c86711a678b9cfb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer (AWS/Azure/GCP | Hybrid Cloud | AI Security)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LifeScale Analytics</t>
+          <t>Storable</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=187fb1dba54e59d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb2c0deb86004e8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Fully Remote!</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KinderCare Learning Companies</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b630719ad31d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=8429c2a459d3de4f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Product Owner II - BI (Memphis, TN or Remote in USA)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Development Infostructure</t>
+          <t>St. Jude Children's Research Hospital</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, API Gateway, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e5739e46621f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=ea984ba020827de7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Santa Cruz, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9216704e953a3254</t>
+          <t>https://www.indeed.com/viewjob?jk=1e946f43c0ce5053</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Santa Cruz, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, Hadoop, Hive, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,102 +1896,102 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; Backend Platform Engineer</t>
+          <t>Senior Software/Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ASU Preparatory Academy</t>
+          <t>CINC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala</t>
+          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, PostgreSQL, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c86711a678b9cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff04daca7022946</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Storable</t>
+          <t>Paradigm Max Q LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb2c0deb86004e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b309f7d0c7f520</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer - Management and Operations (Remote in US)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>Inspire11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126895852cc1414c</t>
+          <t>https://www.indeed.com/viewjob?jk=fcac04dbf474e01b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44f16ef92378b0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GCP ML Engineer (Vertex AI)</t>
+          <t>Front-End Growth Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EvaFi</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Spark</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,137 +2071,137 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce22f8b356b35619</t>
+          <t>https://www.indeed.com/viewjob?jk=658e57cd8469a251</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer, Pro360 Product Group</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NEXON America</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Splunk, Jenkins</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Hadoop, Scala, SQL Server, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b0bc6c388f4a159c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Product Owner II - BI (Memphis, TN or Remote in USA)</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea984ba020827de7</t>
+          <t>https://www.indeed.com/viewjob?jk=70cf81a93ee7ae14</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8429c2a459d3de4f</t>
+          <t>https://www.indeed.com/viewjob?jk=2af3b2ea12351135</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Santa Cruz, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e946f43c0ce5053</t>
+          <t>https://www.indeed.com/viewjob?jk=55dd6036cf4386c2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
+          <t>QA Test Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>RightEye</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Santa Cruz, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, ELT, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd26ece4523f804</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Software Engineer III - UnderwritingCenter</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf763802f514ac89</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4f413a4cd84f6f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Engineer Senior</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, ETL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7c3880bf1468af</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5e0df0ff0f2609</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sales/Solutions Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Inspire11</t>
+          <t>Artie</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcac04dbf474e01b</t>
+          <t>https://www.indeed.com/viewjob?jk=50c1fe1287b79994</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Main Sail, LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44f16ef92378b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5675e83788c1c4fd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Platform Architect - AI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2be041ba7dd258</t>
+          <t>https://www.indeed.com/viewjob?jk=57c71c270f4f024f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Front-End Growth Engineer</t>
+          <t>Senior Data Engineer - Informatica IDMC &amp; CDGC (Data Lineage &amp; Data Quality)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EvaFi</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658e57cd8469a251</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6fa1054166d69d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, API Gateway, Azure, Data Factory, Databricks, Scala, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
+          <t>https://www.indeed.com/viewjob?jk=48a7dc9b2a0c6b63</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4249a3228aea17d</t>
+          <t>https://www.indeed.com/viewjob?jk=c208f65820392c92</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer, Pro360 Product Group</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Hadoop, Scala, SQL Server, ETL, ELT, CI/CD</t>
+          <t>IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bc6c388f4a159c</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f52b7af2ce28a8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Data Engineer – Cloud and AI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,269 +2596,269 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70cf81a93ee7ae14</t>
+          <t>https://www.indeed.com/viewjob?jk=01f85e7d7e897954</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer - Privacy &amp; Governance</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>Pacers Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Data Modeling, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2af3b2ea12351135</t>
+          <t>https://www.indeed.com/viewjob?jk=4b85de9f1c3e87c3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55dd6036cf4386c2</t>
+          <t>https://www.indeed.com/viewjob?jk=58554de2ec8995a5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3f768cf0468176</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer III - UnderwritingCenter</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4f413a4cd84f6f</t>
+          <t>https://www.indeed.com/viewjob?jk=99a2663edcff3f50</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Engineer Senior</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, ETL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5e0df0ff0f2609</t>
+          <t>https://www.indeed.com/viewjob?jk=adbc9cd08b84cd98</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sales/Solutions Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Artie</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c1fe1287b79994</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0bc38b45daf54f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Platform Architect - AI</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57c71c270f4f024f</t>
+          <t>https://www.indeed.com/viewjob?jk=82ce171147829d0d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Informatica IDMC &amp; CDGC (Data Lineage &amp; Data Quality)</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6fa1054166d69d</t>
+          <t>https://www.indeed.com/viewjob?jk=303dbe21162aedcd</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a7dc9b2a0c6b63</t>
+          <t>https://www.indeed.com/viewjob?jk=fe994dfe0ba2aa27</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Avature</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f0d7f99a5b402c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d761590421f49ab</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c208f65820392c92</t>
+          <t>https://www.indeed.com/viewjob?jk=892b50984f957507</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f52b7af2ce28a8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e8225e252d5b308</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer – Cloud and AI</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01f85e7d7e897954</t>
+          <t>https://www.indeed.com/viewjob?jk=410addd619a13132</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
+          <t>https://www.indeed.com/viewjob?jk=39d8229a4579bf54</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Denovo Ventures</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Louisville, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83484ce8e2c739af</t>
+          <t>https://www.indeed.com/viewjob?jk=f3625b9b2eb13247</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Engineer - Full Stack</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, CI/CD, Jenkins, GitHub Actions, Maven, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24fe9813b60c6c14</t>
+          <t>https://www.indeed.com/viewjob?jk=53e23e0d93a166cf</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BeyondTrust</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e471f407b19da8</t>
+          <t>https://www.indeed.com/viewjob?jk=2728055e2c8c11c3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Git</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c2a11252e4d062</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Developer (Systems Software) - TS/SCI w/ Polygraph</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,42 +3251,42 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Scala, ETL, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b918f48362f41a28</t>
+          <t>https://www.indeed.com/viewjob?jk=b216e39afb6b76d8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Informatica IDMC</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,67 +3296,67 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfba15617362e81</t>
+          <t>https://www.indeed.com/viewjob?jk=f3210e4592c9a0d4</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Denovo Ventures</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Louisville, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48debf03335c270f</t>
+          <t>https://www.indeed.com/viewjob?jk=83484ce8e2c739af</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Senior Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, NoSQL, CI/CD, Jenkins, GitHub Actions, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d09fe840e33b4c7</t>
+          <t>https://www.indeed.com/viewjob?jk=24fe9813b60c6c14</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>BeyondTrust</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56229e27f5c6fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=12e471f407b19da8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Software Developer (Systems Software) - TS/SCI w/ Polygraph</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Hadoop, Hive, Scala, ETL, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f39f88a9b70f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=b918f48362f41a28</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Oracle, PostgreSQL, MongoDB, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c41862eb239f163</t>
+          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Remote / Project-Based Data Engineer for Public-Sector Data Modernization, Dashboards, and AI-Ready</t>
+          <t>Senior Data Engineer - Informatica IDMC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, PostgreSQL, MySQL, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f000f4be342c4377</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfba15617362e81</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Serenity Healthcare</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fffc235cb241e45</t>
+          <t>https://www.indeed.com/viewjob?jk=48debf03335c270f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ec2088a10dc04e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d09fe840e33b4c7</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f2031edb48e342e</t>
+          <t>https://www.indeed.com/viewjob?jk=e56229e27f5c6fd1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=569983f090ab2e02</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f39f88a9b70f0a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Remote / Project-Based Data Engineer for Public-Sector Data Modernization, Dashboards, and AI-Ready</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Vidoori</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hyattsville, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, PostgreSQL, MySQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7710e703cc72f4b0</t>
+          <t>https://www.indeed.com/viewjob?jk=f000f4be342c4377</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Serenity Healthcare</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Power BI, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9af17a3ab15e53</t>
+          <t>https://www.indeed.com/viewjob?jk=9fffc235cb241e45</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer</t>
+          <t>Senior Full-Stack Software Engineer (Ruby on Rails) #1148</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>Decisiv Inc</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Babylon, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, Scala, PostgreSQL, ELT, CI/CD, Docker, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d3d24d3399d0363</t>
+          <t>https://www.indeed.com/viewjob?jk=3f91b6ba40d79ba3</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SmartAdvocate</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=001c431f02e0a7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=d656dac9920b857b</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Scientist &amp; Modeler</t>
+          <t>Senior Backend Engineer — ChainIT Pay</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Iberdrola Group</t>
+          <t>ChainIT Pay</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Orange, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Azure, YARN, Scala, Kafka</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39fab587fb046739</t>
+          <t>https://www.indeed.com/viewjob?jk=632c5a674bd9833e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vidoori</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Hyattsville, MD, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Docker, Git, Datadog</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87e755ed281f268b</t>
+          <t>https://www.indeed.com/viewjob?jk=7710e703cc72f4b0</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Scientist (944)</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ABC Supply Co., Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, ETL, ELT, Tableau, MLOps, MLflow, Git, Python</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,7 +3891,147 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2beae7f9c463995</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9af17a3ab15e53</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Product Software Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Wolters Kluwer</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Babylon, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d3d24d3399d0363</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>AI DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SmartAdvocate</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Melville, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=001c431f02e0a7d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist &amp; Modeler</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Iberdrola Group</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Orange, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39fab587fb046739</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Docker, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87e755ed281f268b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-12.xlsx
+++ b/results/job_matches_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, PySpark, ETL, AWS</t>
+          <t>#19675 - Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Qualitest</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e01551f023130f4</t>
+          <t>https://www.indeed.com/viewjob?jk=83236b2299aaa9b3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer III- Python, PySpark, ETL, AWS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,69 +731,69 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, SQS, SNS, RDS, Databricks</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b239490817bb3dba</t>
+          <t>https://www.indeed.com/viewjob?jk=1e01551f023130f4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, SQS, SNS, RDS, Databricks</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8317116e3b8b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b239490817bb3dba</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,77 +801,77 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171403dbdac6e42f</t>
+          <t>https://www.indeed.com/viewjob?jk=50d8317116e3b8b4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI/ML Engineer (Hybrid)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Lightspeed DMS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a2a750b8d45131</t>
+          <t>https://www.indeed.com/viewjob?jk=790fd744b846b460</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5378ca2d10086b6</t>
+          <t>https://www.indeed.com/viewjob?jk=171403dbdac6e42f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>AI/ML Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
+          <t>AWS, Glue, Athena, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d24c78be0131037</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a2a750b8d45131</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer - Java and API Development</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Encore Fire Protection</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Needham, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, MySQL, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9585bb14bb3c50d</t>
+          <t>https://www.indeed.com/viewjob?jk=3110566f2bb6fb7d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4350b7356581efc</t>
+          <t>https://www.indeed.com/viewjob?jk=0d24c78be0131037</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kestra Financial</t>
+          <t>Encore Fire Protection</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Needham, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, MySQL, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4aca5f146dc1fe</t>
+          <t>https://www.indeed.com/viewjob?jk=f9585bb14bb3c50d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kestra Financial</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6cbe9c6196981eb</t>
+          <t>https://www.indeed.com/viewjob?jk=c4350b7356581efc</t>
         </is>
       </c>
     </row>
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9d37985c0bdcf2</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4aca5f146dc1fe</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837e9f344d302e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=c6cbe9c6196981eb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Development Infostructure</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, API Gateway, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e5739e46621f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9d37985c0bdcf2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9216704e953a3254</t>
+          <t>https://www.indeed.com/viewjob?jk=837e9f344d302e6d</t>
         </is>
       </c>
     </row>
@@ -1623,25 +1623,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fuse Fundraising</t>
+          <t>Development Infostructure</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Redshift, S3, API Gateway, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,59 +1651,59 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af281bb5ea90fb04</t>
+          <t>https://www.indeed.com/viewjob?jk=49e5739e46621f5d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer - Management and Operations (Remote in US)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126895852cc1414c</t>
+          <t>https://www.indeed.com/viewjob?jk=9216704e953a3254</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; Backend Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ASU Preparatory Academy</t>
+          <t>Fuse Fundraising</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c86711a678b9cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=af281bb5ea90fb04</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Cloud &amp; Backend Platform Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Storable</t>
+          <t>ASU Preparatory Academy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb2c0deb86004e8</t>
+          <t>https://www.indeed.com/viewjob?jk=4c86711a678b9cfb</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Storable</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8429c2a459d3de4f</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb2c0deb86004e8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Product Owner II - BI (Memphis, TN or Remote in USA)</t>
+          <t>Sr Databricks Data Engineer(Strong Testing Experience)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>Quadrant Technologies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,112 +1816,112 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea984ba020827de7</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ae1d7b6ce452d8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Santa Cruz, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e946f43c0ce5053</t>
+          <t>https://www.indeed.com/viewjob?jk=d799dce46a222f6f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
+          <t>Product Owner II - BI (Memphis, TN or Remote in USA)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>St. Jude Children's Research Hospital</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Santa Cruz, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea984ba020827de7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software/Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CINC</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, PostgreSQL, DynamoDB, Data Modeling, ETL</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff04daca7022946</t>
+          <t>https://www.indeed.com/viewjob?jk=8429c2a459d3de4f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Senior Software/Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Paradigm Max Q LLC</t>
+          <t>CINC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, PostgreSQL, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b309f7d0c7f520</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff04daca7022946</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Inspire11</t>
+          <t>Paradigm Max Q LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcac04dbf474e01b</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b309f7d0c7f520</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Santa Cruz, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44f16ef92378b0</t>
+          <t>https://www.indeed.com/viewjob?jk=1e946f43c0ce5053</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Front-End Growth Engineer</t>
+          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EvaFi</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Santa Cruz, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,102 +2071,102 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658e57cd8469a251</t>
+          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer, Pro360 Product Group</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Cloudera</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Hadoop, Scala, SQL Server, ETL, ELT, CI/CD</t>
+          <t>HDFS, HBase, YARN, Impala, Spark, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bc6c388f4a159c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b3f05e86ef2713f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Developer (Java Full Stack)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70cf81a93ee7ae14</t>
+          <t>https://www.indeed.com/viewjob?jk=441150d8faf9caf5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Front-End Growth Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>EvaFi</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2af3b2ea12351135</t>
+          <t>https://www.indeed.com/viewjob?jk=658e57cd8469a251</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55dd6036cf4386c2</t>
+          <t>https://www.indeed.com/viewjob?jk=256f30d9aec8fc7b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>QA Test Engineer</t>
+          <t>Data Engineer, Pro360 Product Group</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RightEye</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, ELT, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Hadoop, Scala, SQL Server, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd26ece4523f804</t>
+          <t>https://www.indeed.com/viewjob?jk=b0bc6c388f4a159c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer III - UnderwritingCenter</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4f413a4cd84f6f</t>
+          <t>https://www.indeed.com/viewjob?jk=70cf81a93ee7ae14</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Engineer Senior</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, ETL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5e0df0ff0f2609</t>
+          <t>https://www.indeed.com/viewjob?jk=2af3b2ea12351135</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sales/Solutions Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Artie</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c1fe1287b79994</t>
+          <t>https://www.indeed.com/viewjob?jk=55dd6036cf4386c2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Mainframe Systems Analyst / COBOL Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Main Sail, LLC</t>
+          <t>Kalven Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5675e83788c1c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9ec3911362a613</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Platform Architect - AI</t>
+          <t>QA Test Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>RightEye</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,77 +2411,77 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, RDS, ELT, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57c71c270f4f024f</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd26ece4523f804</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Informatica IDMC &amp; CDGC (Data Lineage &amp; Data Quality)</t>
+          <t>Software Engineer III - UnderwritingCenter</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6fa1054166d69d</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4f413a4cd84f6f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Engineer Senior</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, ETL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,102 +2491,102 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a7dc9b2a0c6b63</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5e0df0ff0f2609</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Sales/Solutions Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Artie</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c208f65820392c92</t>
+          <t>https://www.indeed.com/viewjob?jk=50c1fe1287b79994</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>Main Sail, LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f52b7af2ce28a8</t>
+          <t>https://www.indeed.com/viewjob?jk=5675e83788c1c4fd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer – Cloud and AI</t>
+          <t>Platform Architect - AI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01f85e7d7e897954</t>
+          <t>https://www.indeed.com/viewjob?jk=57c71c270f4f024f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Privacy &amp; Governance</t>
+          <t>Performance Test Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pacers Sports &amp; Entertainment</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Data Modeling, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Scala, Oracle, Splunk</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b85de9f1c3e87c3</t>
+          <t>https://www.indeed.com/viewjob?jk=4e993be5e41a8574</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Developer &amp; Data Process Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Voxelmaps</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58554de2ec8995a5</t>
+          <t>https://www.indeed.com/viewjob?jk=194291b22b7de57e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Data Engineer - Informatica IDMC &amp; CDGC (Data Lineage &amp; Data Quality)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Redshift, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3f768cf0468176</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6fa1054166d69d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a2663edcff3f50</t>
+          <t>https://www.indeed.com/viewjob?jk=c208f65820392c92</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbc9cd08b84cd98</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f52b7af2ce28a8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Data Engineer – Cloud and AI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0bc38b45daf54f</t>
+          <t>https://www.indeed.com/viewjob?jk=01f85e7d7e897954</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Data Engineer - Privacy &amp; Governance</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Pacers Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Data Modeling, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ce171147829d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=4b85de9f1c3e87c3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303dbe21162aedcd</t>
+          <t>https://www.indeed.com/viewjob?jk=48a7dc9b2a0c6b63</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe994dfe0ba2aa27</t>
+          <t>https://www.indeed.com/viewjob?jk=58554de2ec8995a5</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d761590421f49ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3f768cf0468176</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892b50984f957507</t>
+          <t>https://www.indeed.com/viewjob?jk=99a2663edcff3f50</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e8225e252d5b308</t>
+          <t>https://www.indeed.com/viewjob?jk=adbc9cd08b84cd98</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410addd619a13132</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0bc38b45daf54f</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d8229a4579bf54</t>
+          <t>https://www.indeed.com/viewjob?jk=82ce171147829d0d</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3625b9b2eb13247</t>
+          <t>https://www.indeed.com/viewjob?jk=303dbe21162aedcd</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53e23e0d93a166cf</t>
+          <t>https://www.indeed.com/viewjob?jk=fe994dfe0ba2aa27</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2728055e2c8c11c3</t>
+          <t>https://www.indeed.com/viewjob?jk=8d761590421f49ab</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c2a11252e4d062</t>
+          <t>https://www.indeed.com/viewjob?jk=892b50984f957507</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b216e39afb6b76d8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e8225e252d5b308</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3210e4592c9a0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=410addd619a13132</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Denovo Ventures</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Louisville, CO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83484ce8e2c739af</t>
+          <t>https://www.indeed.com/viewjob?jk=39d8229a4579bf54</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Engineer - Full Stack</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, CI/CD, Jenkins, GitHub Actions, Maven, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24fe9813b60c6c14</t>
+          <t>https://www.indeed.com/viewjob?jk=f3625b9b2eb13247</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BeyondTrust</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e471f407b19da8</t>
+          <t>https://www.indeed.com/viewjob?jk=53e23e0d93a166cf</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Developer (Systems Software) - TS/SCI w/ Polygraph</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Scala, ETL, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b918f48362f41a28</t>
+          <t>https://www.indeed.com/viewjob?jk=2728055e2c8c11c3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,42 +3461,42 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Git</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c2a11252e4d062</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Informatica IDMC</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,102 +3506,102 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfba15617362e81</t>
+          <t>https://www.indeed.com/viewjob?jk=b216e39afb6b76d8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48debf03335c270f</t>
+          <t>https://www.indeed.com/viewjob?jk=f3210e4592c9a0d4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Denovo Ventures</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Louisville, CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d09fe840e33b4c7</t>
+          <t>https://www.indeed.com/viewjob?jk=83484ce8e2c739af</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Senior Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, NoSQL, CI/CD, Jenkins, GitHub Actions, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56229e27f5c6fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=24fe9813b60c6c14</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BeyondTrust</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f39f88a9b70f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=12e471f407b19da8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Remote / Project-Based Data Engineer for Public-Sector Data Modernization, Dashboards, and AI-Ready</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, PostgreSQL, MySQL, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f000f4be342c4377</t>
+          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer (Systems Software) - TS/SCI w/ Polygraph</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Serenity Healthcare</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Hadoop, Hive, Scala, ETL, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fffc235cb241e45</t>
+          <t>https://www.indeed.com/viewjob?jk=b918f48362f41a28</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer (Ruby on Rails) #1148</t>
+          <t>Senior Data Engineer - Informatica IDMC</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Decisiv Inc</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, ECS, Scala, PostgreSQL, ELT, CI/CD, Docker, Git, Python, SQL</t>
+          <t>AWS, Redshift, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f91b6ba40d79ba3</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfba15617362e81</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,29 +3776,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d656dac9920b857b</t>
+          <t>https://www.indeed.com/viewjob?jk=8d09fe840e33b4c7</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer — ChainIT Pay</t>
+          <t>Remote / Project-Based Data Engineer for Public-Sector Data Modernization, Dashboards, and AI-Ready</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ChainIT Pay</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Azure, YARN, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, PostgreSQL, MySQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632c5a674bd9833e</t>
+          <t>https://www.indeed.com/viewjob?jk=f000f4be342c4377</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Vidoori</t>
+          <t>Serenity Healthcare</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hyattsville, MD, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7710e703cc72f4b0</t>
+          <t>https://www.indeed.com/viewjob?jk=9fffc235cb241e45</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Power BI, Git, Python, SQL</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9af17a3ab15e53</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f39f88a9b70f0a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Babylon, NY, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d3d24d3399d0363</t>
+          <t>https://www.indeed.com/viewjob?jk=48debf03335c270f</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SmartAdvocate</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Jenkins</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=001c431f02e0a7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e56229e27f5c6fd1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Scientist &amp; Modeler</t>
+          <t>Senior Full-Stack Software Engineer (Ruby on Rails) #1148</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Iberdrola Group</t>
+          <t>Decisiv Inc</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Orange, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, ECS, Scala, PostgreSQL, ELT, CI/CD, Docker, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39fab587fb046739</t>
+          <t>https://www.indeed.com/viewjob?jk=3f91b6ba40d79ba3</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,15 +4021,295 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d656dac9920b857b</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer — ChainIT Pay</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ChainIT Pay</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Azure, YARN, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=632c5a674bd9833e</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Business System Analyst II</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Williams-Sonoma, Inc.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Redshift, IAM, RDS, Databricks, Scala, Snowflake, Oracle, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd9fce2d50998712</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Business System Analyst</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Williams-Sonoma, Inc.</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Redshift, IAM, RDS, Databricks, Scala, Snowflake, Oracle, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cde11141186b52e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Vidoori</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Hyattsville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7710e703cc72f4b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Azure Data Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Power BI, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc9af17a3ab15e53</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Product Software Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Wolters Kluwer</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Babylon, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d3d24d3399d0363</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>AI DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SmartAdvocate</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Melville, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=001c431f02e0a7d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
           <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Docker, Git, Datadog</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=87e755ed281f268b</t>
         </is>

--- a/results/job_matches_2026-05-12.xlsx
+++ b/results/job_matches_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Systems Engineer, UDS Data Management - East</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6fb94b58173aba</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1f7dab55752b3e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management - East</t>
+          <t>#19675 - Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Qualitest</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1f7dab55752b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=83236b2299aaa9b3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>#19675 - Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Qualitest</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, SQS, SNS, RDS, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83236b2299aaa9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=b239490817bb3dba</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, PySpark, ETL, AWS</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e01551f023130f4</t>
+          <t>https://www.indeed.com/viewjob?jk=50d8317116e3b8b4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Lightspeed DMS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, SQS, SNS, RDS, Databricks</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b239490817bb3dba</t>
+          <t>https://www.indeed.com/viewjob?jk=790fd744b846b460</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>AI/ML Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, Glue, Athena, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8317116e3b8b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a2a750b8d45131</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lightspeed DMS</t>
+          <t>POWERX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=790fd744b846b460</t>
+          <t>https://www.indeed.com/viewjob?jk=78d222e67b861731</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Sr Software Engineer - Java and API Development</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171403dbdac6e42f</t>
+          <t>https://www.indeed.com/viewjob?jk=3110566f2bb6fb7d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI/ML Engineer (Hybrid)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake</t>
+          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a2a750b8d45131</t>
+          <t>https://www.indeed.com/viewjob?jk=0d24c78be0131037</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Java and API Development</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Encore Fire Protection</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Needham, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, MySQL, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3110566f2bb6fb7d</t>
+          <t>https://www.indeed.com/viewjob?jk=f9585bb14bb3c50d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d24c78be0131037</t>
+          <t>https://www.indeed.com/viewjob?jk=c4350b7356581efc</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Encore Fire Protection</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Needham, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, MySQL, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9585bb14bb3c50d</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4aca5f146dc1fe</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4350b7356581efc</t>
+          <t>https://www.indeed.com/viewjob?jk=c6cbe9c6196981eb</t>
         </is>
       </c>
     </row>
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4aca5f146dc1fe</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9d37985c0bdcf2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Cloud Security Engineer (AWS/Azure/GCP | Hybrid Cloud | AI Security)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kestra Financial</t>
+          <t>LifeScale Analytics</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Glue, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6cbe9c6196981eb</t>
+          <t>https://www.indeed.com/viewjob?jk=187fb1dba54e59d2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Machine Learning Engineer - Fully Remote!</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kestra Financial</t>
+          <t>KinderCare Learning Companies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9d37985c0bdcf2</t>
+          <t>https://www.indeed.com/viewjob?jk=38b630719ad31d3a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Development Infostructure</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Redshift, S3, API Gateway, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837e9f344d302e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=49e5739e46621f5d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer (AWS/Azure/GCP | Hybrid Cloud | AI Security)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LifeScale Analytics</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,102 +1581,102 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=187fb1dba54e59d2</t>
+          <t>https://www.indeed.com/viewjob?jk=9216704e953a3254</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Fully Remote!</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>KinderCare Learning Companies</t>
+          <t>Fuse Fundraising</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b630719ad31d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=af281bb5ea90fb04</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Senior Cloud &amp; Backend Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Development Infostructure</t>
+          <t>ASU Preparatory Academy</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, API Gateway, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e5739e46621f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=4c86711a678b9cfb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Storable</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9216704e953a3254</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb2c0deb86004e8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Databricks Data Engineer(Strong Testing Experience)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fuse Fundraising</t>
+          <t>Quadrant Technologies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af281bb5ea90fb04</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ae1d7b6ce452d8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; Backend Platform Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ASU Preparatory Academy</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c86711a678b9cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=d799dce46a222f6f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Product Owner II - BI (Memphis, TN or Remote in USA)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Storable</t>
+          <t>St. Jude Children's Research Hospital</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb2c0deb86004e8</t>
+          <t>https://www.indeed.com/viewjob?jk=ea984ba020827de7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer(Strong Testing Experience)</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Quadrant Technologies</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ae1d7b6ce452d8</t>
+          <t>https://www.indeed.com/viewjob?jk=8429c2a459d3de4f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Sr. Software Engineer, Popeyes</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>Popeyes</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,94 +1861,94 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d799dce46a222f6f</t>
+          <t>https://www.indeed.com/viewjob?jk=06d9d4b732d1aa48</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Product Owner II - BI (Memphis, TN or Remote in USA)</t>
+          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Santa Cruz, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea984ba020827de7</t>
+          <t>https://www.indeed.com/viewjob?jk=1e946f43c0ce5053</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Santa Cruz, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8429c2a459d3de4f</t>
+          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software/Data Engineer</t>
+          <t>Cloud &amp; Database Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CINC</t>
+          <t>enChoice, Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, PostgreSQL, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Cloud Storage, Scala, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff04daca7022946</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7de1e2049e683c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Senior Software/Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Paradigm Max Q LLC</t>
+          <t>CINC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, PostgreSQL, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b309f7d0c7f520</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff04daca7022946</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>Paradigm Max Q LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Santa Cruz, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e946f43c0ce5053</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b309f7d0c7f520</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>Cloudera</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Santa Cruz, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>HDFS, HBase, YARN, Impala, Spark, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b3f05e86ef2713f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Developer (Java Full Stack)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cloudera</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>HDFS, HBase, YARN, Impala, Spark, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b3f05e86ef2713f</t>
+          <t>https://www.indeed.com/viewjob?jk=441150d8faf9caf5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Developer (Java Full Stack)</t>
+          <t>Front-End Growth Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>EvaFi</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,52 +2131,52 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=441150d8faf9caf5</t>
+          <t>https://www.indeed.com/viewjob?jk=658e57cd8469a251</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Front-End Growth Engineer</t>
+          <t>Senior Data Engineer _ Python with Spark</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EvaFi</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658e57cd8469a251</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8b463a5152c979</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2af3b2ea12351135</t>
+          <t>https://www.indeed.com/viewjob?jk=ef992c4b82254a86</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55dd6036cf4386c2</t>
+          <t>https://www.indeed.com/viewjob?jk=56fdee09cb474dc8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Mainframe Systems Analyst / COBOL Developer</t>
+          <t>API Developer (Java and Micron Experience)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kalven Technologies</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9ec3911362a613</t>
+          <t>https://www.indeed.com/viewjob?jk=867ba74673f5a7f6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>QA Test Engineer</t>
+          <t>Senior Mainframe Systems Analyst / COBOL Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RightEye</t>
+          <t>Kalven Technologies</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, ELT, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd26ece4523f804</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9ec3911362a613</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III - UnderwritingCenter</t>
+          <t>Sales/Solutions Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Artie</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4f413a4cd84f6f</t>
+          <t>https://www.indeed.com/viewjob?jk=50c1fe1287b79994</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Engineer Senior</t>
+          <t>Software Engineer III - UnderwritingCenter</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, ETL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5e0df0ff0f2609</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4f413a4cd84f6f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sales/Solutions Engineer</t>
+          <t>Engineer Senior</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Artie</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, ETL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c1fe1287b79994</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5e0df0ff0f2609</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Performance Test Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Scala, Oracle, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e993be5e41a8574</t>
+          <t>https://www.indeed.com/viewjob?jk=c48f8e75c6761842</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Developer &amp; Data Process Engineer</t>
+          <t>Senior Data Engineer - Informatica IDMC &amp; CDGC (Data Lineage &amp; Data Quality)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Voxelmaps</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Airflow</t>
+          <t>AWS, Redshift, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=194291b22b7de57e</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6fa1054166d69d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Informatica IDMC &amp; CDGC (Data Lineage &amp; Data Quality)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6fa1054166d69d</t>
+          <t>https://www.indeed.com/viewjob?jk=48a7dc9b2a0c6b63</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>RXO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c208f65820392c92</t>
+          <t>https://www.indeed.com/viewjob?jk=eedaefa82474ae57</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Performance Test Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Scala, Oracle, Splunk</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f52b7af2ce28a8</t>
+          <t>https://www.indeed.com/viewjob?jk=4e993be5e41a8574</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer – Cloud and AI</t>
+          <t>Developer &amp; Data Process Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Voxelmaps</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01f85e7d7e897954</t>
+          <t>https://www.indeed.com/viewjob?jk=194291b22b7de57e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Privacy &amp; Governance</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pacers Sports &amp; Entertainment</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Data Modeling, dbt, Power BI, Tableau, CI/CD</t>
+          <t>IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b85de9f1c3e87c3</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f52b7af2ce28a8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer – Cloud and AI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a7dc9b2a0c6b63</t>
+          <t>https://www.indeed.com/viewjob?jk=01f85e7d7e897954</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Data Engineer - Privacy &amp; Governance</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Pacers Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Data Modeling, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58554de2ec8995a5</t>
+          <t>https://www.indeed.com/viewjob?jk=4b85de9f1c3e87c3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Synctera</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, dbt, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3f768cf0468176</t>
+          <t>https://www.indeed.com/viewjob?jk=de5f0f370de70f71</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a2663edcff3f50</t>
+          <t>https://www.indeed.com/viewjob?jk=58554de2ec8995a5</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbc9cd08b84cd98</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3f768cf0468176</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0bc38b45daf54f</t>
+          <t>https://www.indeed.com/viewjob?jk=99a2663edcff3f50</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ce171147829d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=adbc9cd08b84cd98</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303dbe21162aedcd</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0bc38b45daf54f</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe994dfe0ba2aa27</t>
+          <t>https://www.indeed.com/viewjob?jk=82ce171147829d0d</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d761590421f49ab</t>
+          <t>https://www.indeed.com/viewjob?jk=303dbe21162aedcd</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892b50984f957507</t>
+          <t>https://www.indeed.com/viewjob?jk=fe994dfe0ba2aa27</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e8225e252d5b308</t>
+          <t>https://www.indeed.com/viewjob?jk=8d761590421f49ab</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410addd619a13132</t>
+          <t>https://www.indeed.com/viewjob?jk=892b50984f957507</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d8229a4579bf54</t>
+          <t>https://www.indeed.com/viewjob?jk=6e8225e252d5b308</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3625b9b2eb13247</t>
+          <t>https://www.indeed.com/viewjob?jk=410addd619a13132</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53e23e0d93a166cf</t>
+          <t>https://www.indeed.com/viewjob?jk=39d8229a4579bf54</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2728055e2c8c11c3</t>
+          <t>https://www.indeed.com/viewjob?jk=f3625b9b2eb13247</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c2a11252e4d062</t>
+          <t>https://www.indeed.com/viewjob?jk=53e23e0d93a166cf</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b216e39afb6b76d8</t>
+          <t>https://www.indeed.com/viewjob?jk=2728055e2c8c11c3</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3210e4592c9a0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c2a11252e4d062</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Denovo Ventures</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Louisville, CO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83484ce8e2c739af</t>
+          <t>https://www.indeed.com/viewjob?jk=b216e39afb6b76d8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Engineer - Full Stack</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, CI/CD, Jenkins, GitHub Actions, Maven, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24fe9813b60c6c14</t>
+          <t>https://www.indeed.com/viewjob?jk=f3210e4592c9a0d4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Senior Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BeyondTrust</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, NoSQL, CI/CD, Jenkins, GitHub Actions, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e471f407b19da8</t>
+          <t>https://www.indeed.com/viewjob?jk=24fe9813b60c6c14</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>BeyondTrust</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
+          <t>https://www.indeed.com/viewjob?jk=12e471f407b19da8</t>
         </is>
       </c>
     </row>
@@ -3723,25 +3723,25 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Informatica IDMC</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfba15617362e81</t>
+          <t>https://www.indeed.com/viewjob?jk=7635d54e2c34fa9c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>DevOps Engineer- Ashburn, VA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ellumen, Inc</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d09fe840e33b4c7</t>
+          <t>https://www.indeed.com/viewjob?jk=797eb835c7f60f42</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Remote / Project-Based Data Engineer for Public-Sector Data Modernization, Dashboards, and AI-Ready</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SilverEdge Government Solutions</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, PostgreSQL, MySQL, ETL, ELT, Power BI</t>
+          <t>AWS, ECS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f000f4be342c4377</t>
+          <t>https://www.indeed.com/viewjob?jk=8db426b190d5761e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Informatica IDMC</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Serenity Healthcare</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, Redshift, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fffc235cb241e45</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfba15617362e81</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f39f88a9b70f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=48debf03335c270f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48debf03335c270f</t>
+          <t>https://www.indeed.com/viewjob?jk=8d09fe840e33b4c7</t>
         </is>
       </c>
     </row>
@@ -3968,17 +3968,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer (Ruby on Rails) #1148</t>
+          <t>Senior Financial Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Decisiv Inc</t>
+          <t>cpg.io eCommerce Distributors</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Addison, IL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, ECS, Scala, PostgreSQL, ELT, CI/CD, Docker, Git, Python, SQL</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,19 +3996,19 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f91b6ba40d79ba3</t>
+          <t>https://www.indeed.com/viewjob?jk=a84dfece3c2e1aec</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Backend Engineer — ChainIT Pay</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>ChainIT Pay</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Azure, YARN, Scala, Kafka</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,19 +4031,19 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d656dac9920b857b</t>
+          <t>https://www.indeed.com/viewjob?jk=632c5a674bd9833e</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer — ChainIT Pay</t>
+          <t>Senior Full-Stack Software Engineer (Ruby on Rails) #1148</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ChainIT Pay</t>
+          <t>Decisiv Inc</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Azure, YARN, Scala, Kafka</t>
+          <t>AWS, ECS, Scala, PostgreSQL, ELT, CI/CD, Docker, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632c5a674bd9833e</t>
+          <t>https://www.indeed.com/viewjob?jk=3f91b6ba40d79ba3</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Business System Analyst II</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Williams-Sonoma, Inc.</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Databricks, Scala, Snowflake, Oracle, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9fce2d50998712</t>
+          <t>https://www.indeed.com/viewjob?jk=d656dac9920b857b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Business System Analyst</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Williams-Sonoma, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Databricks, Scala, Snowflake, Oracle, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Docker, Git, Datadog</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde11141186b52e3</t>
+          <t>https://www.indeed.com/viewjob?jk=87e755ed281f268b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Vidoori</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hyattsville, MD, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7710e703cc72f4b0</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9af17a3ab15e53</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Vidoori</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Hyattsville, MD, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Power BI, Git, Python, SQL</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9af17a3ab15e53</t>
+          <t>https://www.indeed.com/viewjob?jk=7710e703cc72f4b0</t>
         </is>
       </c>
     </row>
@@ -4242,76 +4242,6 @@
       <c r="G109" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3d3d24d3399d0363</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>AI DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>SmartAdvocate</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Melville, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=001c431f02e0a7d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Glendale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Docker, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87e755ed281f268b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-12.xlsx
+++ b/results/job_matches_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full-Stack Senior Software Engineer</t>
+          <t>Sr Engineer, Ent Arch</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Asurion</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, S3, SNS, IAM, RDS, Azure, Cloud Storage, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f3191cc3d47286</t>
+          <t>https://www.indeed.com/viewjob?jk=618fbf33fe541db8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - Optum Advisory Board - Remote</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dff403bb7c12a386</t>
+          <t>https://www.indeed.com/viewjob?jk=7b20e14df8f336ad</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Optum Advisory Board - Remote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Benchmark Solutions LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8cfebbb7e871628</t>
+          <t>https://www.indeed.com/viewjob?jk=dff403bb7c12a386</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Data Engineer – Baltimore City, MD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1df3e0ee29922c</t>
+          <t>https://www.indeed.com/viewjob?jk=80ac3e71ab2ea33f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management - East</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Benchmark Solutions LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1f7dab55752b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8cfebbb7e871628</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>#19675 - Data Engineer</t>
+          <t>Senior Systems Engineer, UDS Data Management - East</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Qualitest</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83236b2299aaa9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1f7dab55752b3e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>#19675 - Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Qualitest</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,69 +696,69 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, SQS, SNS, RDS, Databricks</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b239490817bb3dba</t>
+          <t>https://www.indeed.com/viewjob?jk=83236b2299aaa9b3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, SQS, SNS, RDS, Databricks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8317116e3b8b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b239490817bb3dba</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lightspeed DMS</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=790fd744b846b460</t>
+          <t>https://www.indeed.com/viewjob?jk=50d8317116e3b8b4</t>
         </is>
       </c>
     </row>
@@ -853,87 +853,87 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Java and API Development</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, PostgreSQL, MySQL</t>
+          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3110566f2bb6fb7d</t>
+          <t>https://www.indeed.com/viewjob?jk=0d24c78be0131037</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d24c78be0131037</t>
+          <t>https://www.indeed.com/viewjob?jk=110879d3c05b187b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Encore Fire Protection</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Needham, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, MySQL, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9585bb14bb3c50d</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa4c8179a8ac4da</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4350b7356581efc</t>
+          <t>https://www.indeed.com/viewjob?jk=f66f1fbb6c8a1a3b</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110879d3c05b187b</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc984a42640329e</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa4c8179a8ac4da</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfdcd1adce614e6</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66f1fbb6c8a1a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=bd3763e7b5c9b674</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc984a42640329e</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb6a218ca916697</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfdcd1adce614e6</t>
+          <t>https://www.indeed.com/viewjob?jk=d791e762f6d81f87</t>
         </is>
       </c>
     </row>
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd3763e7b5c9b674</t>
+          <t>https://www.indeed.com/viewjob?jk=7943d064127358c8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb6a218ca916697</t>
+          <t>https://www.indeed.com/viewjob?jk=14e64b70ed3febe9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Encore Fire Protection</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Needham, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, MySQL, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d791e762f6d81f87</t>
+          <t>https://www.indeed.com/viewjob?jk=f9585bb14bb3c50d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7943d064127358c8</t>
+          <t>https://www.indeed.com/viewjob?jk=c4350b7356581efc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Kestra Financial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e64b70ed3febe9</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4aca5f146dc1fe</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4aca5f146dc1fe</t>
+          <t>https://www.indeed.com/viewjob?jk=c6cbe9c6196981eb</t>
         </is>
       </c>
     </row>
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6cbe9c6196981eb</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9d37985c0bdcf2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kestra Financial</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9d37985c0bdcf2</t>
+          <t>https://www.indeed.com/viewjob?jk=8348059168d7d3ed</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Fully Remote!</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KinderCare Learning Companies</t>
+          <t>Development Infostructure</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>AWS, Redshift, S3, API Gateway, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b630719ad31d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=49e5739e46621f5d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Development Infostructure</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,69 +1536,69 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, API Gateway, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e5739e46621f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=9216704e953a3254</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Fuse Fundraising</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9216704e953a3254</t>
+          <t>https://www.indeed.com/viewjob?jk=af281bb5ea90fb04</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud &amp; Backend Platform Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fuse Fundraising</t>
+          <t>ASU Preparatory Academy</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af281bb5ea90fb04</t>
+          <t>https://www.indeed.com/viewjob?jk=4c86711a678b9cfb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; Backend Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ASU Preparatory Academy</t>
+          <t>Storable</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c86711a678b9cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb2c0deb86004e8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Storable</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb2c0deb86004e8</t>
+          <t>https://www.indeed.com/viewjob?jk=de13e412e9eb12ce</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Popeyes</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Popeyes</t>
+          <t>ifm efector inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06d9d4b732d1aa48</t>
+          <t>https://www.indeed.com/viewjob?jk=c320ee229f995ad4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
+          <t>Azure Data Fabric Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>SLD TECHNOLOGIES LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Santa Cruz, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e946f43c0ce5053</t>
+          <t>https://www.indeed.com/viewjob?jk=bb01ba3a845df915</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
+          <t>Cloud &amp; Database Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>enChoice, Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Santa Cruz, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Cloud Storage, Scala, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7de1e2049e683c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud &amp; Database Engineer</t>
+          <t>Senior Software/Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>enChoice, Inc.</t>
+          <t>CINC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Cloud Storage, Scala, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, PostgreSQL, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7de1e2049e683c</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff04daca7022946</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software/Data Engineer</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CINC</t>
+          <t>Paradigm Max Q LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, PostgreSQL, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff04daca7022946</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b309f7d0c7f520</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Paradigm Max Q LLC</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Santa Cruz, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b309f7d0c7f520</t>
+          <t>https://www.indeed.com/viewjob?jk=1e946f43c0ce5053</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Sr. Software Engineer, Popeyes</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cloudera</t>
+          <t>Popeyes</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>HDFS, HBase, YARN, Impala, Spark, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b3f05e86ef2713f</t>
+          <t>https://www.indeed.com/viewjob?jk=06d9d4b732d1aa48</t>
         </is>
       </c>
     </row>
@@ -2113,35 +2113,35 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Front-End Growth Engineer</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EvaFi</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658e57cd8469a251</t>
+          <t>https://www.indeed.com/viewjob?jk=1b780cbd54e20e82</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Backend Software Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef992c4b82254a86</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c70bbdfbf97a8c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770392</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56fdee09cb474dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6a7bc10ac96c1a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>API Developer (Java and Micron Experience)</t>
+          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770393</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=867ba74673f5a7f6</t>
+          <t>https://www.indeed.com/viewjob?jk=23c054ad41fdd40c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Mainframe Systems Analyst / COBOL Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Kalven Technologies</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9ec3911362a613</t>
+          <t>https://www.indeed.com/viewjob?jk=ef992c4b82254a86</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sales/Solutions Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Artie</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c1fe1287b79994</t>
+          <t>https://www.indeed.com/viewjob?jk=56fdee09cb474dc8</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Sales/Solutions Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Main Sail, LLC</t>
+          <t>Artie</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5675e83788c1c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=50c1fe1287b79994</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Platform Architect - AI</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>Main Sail, LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,69 +2586,69 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57c71c270f4f024f</t>
+          <t>https://www.indeed.com/viewjob?jk=5675e83788c1c4fd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Architect - AI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48f8e75c6761842</t>
+          <t>https://www.indeed.com/viewjob?jk=57c71c270f4f024f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Informatica IDMC &amp; CDGC (Data Lineage &amp; Data Quality)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6fa1054166d69d</t>
+          <t>https://www.indeed.com/viewjob?jk=c48f8e75c6761842</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>RXO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a7dc9b2a0c6b63</t>
+          <t>https://www.indeed.com/viewjob?jk=eedaefa82474ae57</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Performance Test Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RXO</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Scala, Oracle, Splunk</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eedaefa82474ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=4e993be5e41a8574</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Performance Test Engineer</t>
+          <t>Developer &amp; Data Process Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>Voxelmaps</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Scala, Oracle, Splunk</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e993be5e41a8574</t>
+          <t>https://www.indeed.com/viewjob?jk=194291b22b7de57e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Developer &amp; Data Process Engineer</t>
+          <t>Senior Data Engineer - Informatica IDMC &amp; CDGC (Data Lineage &amp; Data Quality)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Voxelmaps</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Airflow</t>
+          <t>AWS, Redshift, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=194291b22b7de57e</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6fa1054166d69d</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Synctera</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, dbt, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5f0f370de70f71</t>
+          <t>https://www.indeed.com/viewjob?jk=48a7dc9b2a0c6b63</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Urban Dynamics</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58554de2ec8995a5</t>
+          <t>https://www.indeed.com/viewjob?jk=775f202a52a009bf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Software Engineer (Python, Kafka / Confluent)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3f768cf0468176</t>
+          <t>https://www.indeed.com/viewjob?jk=88b144ea348f35fc</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, NoSQL, CI/CD, Jenkins, GitHub Actions, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a2663edcff3f50</t>
+          <t>https://www.indeed.com/viewjob?jk=24fe9813b60c6c14</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>BeyondTrust</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbc9cd08b84cd98</t>
+          <t>https://www.indeed.com/viewjob?jk=12e471f407b19da8</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0bc38b45daf54f</t>
+          <t>https://www.indeed.com/viewjob?jk=58554de2ec8995a5</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ce171147829d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3f768cf0468176</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303dbe21162aedcd</t>
+          <t>https://www.indeed.com/viewjob?jk=99a2663edcff3f50</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe994dfe0ba2aa27</t>
+          <t>https://www.indeed.com/viewjob?jk=adbc9cd08b84cd98</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d761590421f49ab</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0bc38b45daf54f</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892b50984f957507</t>
+          <t>https://www.indeed.com/viewjob?jk=82ce171147829d0d</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e8225e252d5b308</t>
+          <t>https://www.indeed.com/viewjob?jk=303dbe21162aedcd</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410addd619a13132</t>
+          <t>https://www.indeed.com/viewjob?jk=fe994dfe0ba2aa27</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d8229a4579bf54</t>
+          <t>https://www.indeed.com/viewjob?jk=8d761590421f49ab</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3625b9b2eb13247</t>
+          <t>https://www.indeed.com/viewjob?jk=892b50984f957507</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53e23e0d93a166cf</t>
+          <t>https://www.indeed.com/viewjob?jk=6e8225e252d5b308</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2728055e2c8c11c3</t>
+          <t>https://www.indeed.com/viewjob?jk=410addd619a13132</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c2a11252e4d062</t>
+          <t>https://www.indeed.com/viewjob?jk=39d8229a4579bf54</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b216e39afb6b76d8</t>
+          <t>https://www.indeed.com/viewjob?jk=f3625b9b2eb13247</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3210e4592c9a0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=53e23e0d93a166cf</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Engineer - Full Stack</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, CI/CD, Jenkins, GitHub Actions, Maven, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24fe9813b60c6c14</t>
+          <t>https://www.indeed.com/viewjob?jk=2728055e2c8c11c3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BeyondTrust</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e471f407b19da8</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c2a11252e4d062</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Developer (Systems Software) - TS/SCI w/ Polygraph</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Scala, ETL, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b918f48362f41a28</t>
+          <t>https://www.indeed.com/viewjob?jk=b216e39afb6b76d8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7635d54e2c34fa9c</t>
+          <t>https://www.indeed.com/viewjob?jk=f3210e4592c9a0d4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DevOps Engineer- Ashburn, VA</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ellumen, Inc</t>
+          <t>Synctera</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, dbt, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=797eb835c7f60f42</t>
+          <t>https://www.indeed.com/viewjob?jk=de5f0f370de70f71</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Developer (Systems Software) - TS/SCI w/ Polygraph</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SilverEdge Government Solutions</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Hive, Scala, ETL, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db426b190d5761e</t>
+          <t>https://www.indeed.com/viewjob?jk=b918f48362f41a28</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Informatica IDMC</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>National Basketball Association</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL, dbt, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfba15617362e81</t>
+          <t>https://www.indeed.com/viewjob?jk=7e327a1ee260319b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Financial Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>cpg.io eCommerce Distributors</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Addison, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48debf03335c270f</t>
+          <t>https://www.indeed.com/viewjob?jk=a84dfece3c2e1aec</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Senior Data Engineer - Informatica IDMC</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, Redshift, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d09fe840e33b4c7</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfba15617362e81</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56229e27f5c6fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=8d09fe840e33b4c7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Financial Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>cpg.io eCommerce Distributors</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Addison, IL, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84dfece3c2e1aec</t>
+          <t>https://www.indeed.com/viewjob?jk=48debf03335c270f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer — ChainIT Pay</t>
+          <t>Junior Automation Tester (AI enabled Testing)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ChainIT Pay</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Azure, YARN, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632c5a674bd9833e</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3c372f8cf8158e</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer (Ruby on Rails) #1148</t>
+          <t>Python Engineer with REST &amp; GenAI</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Decisiv Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, ECS, Scala, PostgreSQL, ELT, CI/CD, Docker, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,19 +4066,19 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f91b6ba40d79ba3</t>
+          <t>https://www.indeed.com/viewjob?jk=c3132514d774e51d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Backend Engineer — ChainIT Pay</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>ChainIT Pay</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Azure, YARN, Scala, Kafka</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d656dac9920b857b</t>
+          <t>https://www.indeed.com/viewjob?jk=632c5a674bd9833e</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Docker, Git, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87e755ed281f268b</t>
+          <t>https://www.indeed.com/viewjob?jk=d656dac9920b857b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Vidoori</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Hyattsville, MD, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Power BI, Git, Python, SQL</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9af17a3ab15e53</t>
+          <t>https://www.indeed.com/viewjob?jk=7710e703cc72f4b0</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Vidoori</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hyattsville, MD, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7710e703cc72f4b0</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9af17a3ab15e53</t>
         </is>
       </c>
     </row>
@@ -4242,6 +4242,41 @@
       <c r="G109" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3d3d24d3399d0363</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Docker, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87e755ed281f268b</t>
         </is>
       </c>
     </row>
